--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Platforms'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Services'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>21</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>4</v>
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>20</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
@@ -1074,7 +1074,11 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1146,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2316,7 +2320,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Date &amp; Session Selection</t>
+          <t>Date &amp; Performance Selection</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2479,7 +2483,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the app, fast, on a device that may be shared.</t>
+          <t>Get a guest into the site, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO and no second factor at sign-in for guests** (decided 28 September, audit R167).</t>
         </is>
       </c>
     </row>
@@ -3216,20 +3220,20 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>Wishlist</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Queue calls, order updates, venue notices.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3245,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Wishlist</t>
+          <t>Devices, Wishlist &amp; Consent</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
@@ -3254,7 +3258,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>See loyalty &amp; rewards for this venue.</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3270,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Devices, Wishlist &amp; Consent</t>
+          <t>Survey &amp; Feedback</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
@@ -3279,7 +3283,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>See loyalty &amp; rewards for this venue.</t>
+          <t>Work with survey &amp; feedback for this venue.</t>
         </is>
       </c>
     </row>
@@ -3291,12 +3295,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Survey &amp; Feedback</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
@@ -3304,32 +3308,32 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Work with survey &amp; feedback for this venue.</t>
+          <t>Report something you left behind.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Web</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Home – Default</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Report something you left behind.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3345,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Home – Default</t>
+          <t>Explore Categories</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3354,7 +3358,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Find explore categories for this venue.</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Explore Categories</t>
+          <t>Event &amp; Attraction Listing</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3379,7 +3383,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Find explore categories for this venue.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3395,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Event &amp; Attraction Listing</t>
+          <t>Attraction Details</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3404,7 +3408,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>See attraction details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3420,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Attraction Details</t>
+          <t>What's On</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3429,7 +3433,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>See attraction details for this venue.</t>
+          <t>Find what's on for this venue.</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3445,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>What's On</t>
+          <t>Event / Exhibition Details</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3454,7 +3458,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Find what's on for this venue.</t>
+          <t>See event / exhibition details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3470,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Event / Exhibition Details</t>
+          <t>Select Date &amp; Time</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
@@ -3479,7 +3483,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>See event / exhibition details for this venue.</t>
+          <t>See select date &amp; time for this venue.</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3495,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Select Date &amp; Time</t>
+          <t>Tickets &amp; Add-ons</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3504,7 +3508,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>See select date &amp; time for this venue.</t>
+          <t>Find tickets &amp; add-ons for this venue.</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3520,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Tickets &amp; Add-ons</t>
+          <t>Review &amp; Payment</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
@@ -3529,7 +3533,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Find tickets &amp; add-ons for this venue.</t>
+          <t>Check what you are buying and pay for it.</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3545,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Review &amp; Payment</t>
+          <t>Booking Confirmation</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3554,7 +3558,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Check what you are buying and pay for it.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3570,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Booking Confirmation</t>
+          <t>My Tickets</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
@@ -3579,7 +3583,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>Find my tickets for this venue.</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>My Tickets</t>
+          <t>Ticket Details</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3604,7 +3608,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>Find ticket details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Ticket Details</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3629,7 +3633,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Find ticket details for this venue.</t>
+          <t>What we hold about a guest, and what they can change.</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3645,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Checkout Entry</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
@@ -3654,7 +3658,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>What we hold about a guest, and what they can change.</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -3666,12 +3670,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Checkout Entry</t>
+          <t>Simple Registration &amp; OTP</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
@@ -3679,7 +3683,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO and no second factor at sign-in for guests** (decided 28 September, audit R167).</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3695,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Simple Registration &amp; OTP</t>
+          <t>Arabic / RTL Experience</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Work with simple registration &amp; otp for this venue.</t>
+          <t>Arabic / RTL Experience — the screen a person opens when they need to deal with arabic / rtl experience.</t>
         </is>
       </c>
     </row>
@@ -3716,12 +3720,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
@@ -3729,7 +3733,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience — the screen a person opens when they need to deal with arabic / rtl experience.</t>
+          <t>Find branded queue / waiting room for this venue.</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3745,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Maintenance / Upgrade Page</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
@@ -3754,7 +3758,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Find branded queue / waiting room for this venue.</t>
+          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3770,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Maintenance / Upgrade Page</t>
+          <t>Dynamic QR Ticket</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
@@ -3779,7 +3783,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
+          <t>Find dynamic qr ticket for this venue.</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3795,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Dynamic QR Ticket</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
@@ -3804,7 +3808,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Find dynamic qr ticket for this venue.</t>
+          <t>Find something when you do not know what it is called.</t>
         </is>
       </c>
     </row>
@@ -3816,20 +3820,20 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Wallet Overview</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Find something when you do not know what it is called.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3845,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Wallet Overview</t>
+          <t>Ticket Transfer</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
@@ -3854,7 +3858,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Work with ticket transfer for this venue.</t>
         </is>
       </c>
     </row>
@@ -3866,12 +3870,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Ticket Transfer</t>
+          <t>Memberships</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
@@ -3879,7 +3883,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Work with ticket transfer for this venue.</t>
+          <t>Find memberships for this venue.</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3895,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Memberships</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
@@ -3904,7 +3908,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Find memberships for this venue.</t>
+          <t>Find my reservations for this venue.</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3920,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Reservation Details</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -3929,7 +3933,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Find my reservations for this venue.</t>
+          <t>See reservation details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3945,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Reservation Details</t>
+          <t>Order History</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
@@ -3954,7 +3958,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>See reservation details for this venue.</t>
+          <t>Find order history (wallet) for this venue.</t>
         </is>
       </c>
     </row>
@@ -3966,12 +3970,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Order History</t>
+          <t>Interactive Map</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
@@ -3979,7 +3983,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Find order history (wallet) for this venue.</t>
+          <t>See where things are in relation to each other.</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3995,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Interactive Map</t>
+          <t>Attraction Wait Times</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4004,7 +4008,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>See where things are in relation to each other.</t>
+          <t>See attraction wait times for this venue.</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4020,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Attraction Wait Times</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4029,7 +4033,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>See attraction wait times for this venue.</t>
+          <t>Order food to where the guest is sitting, or for collection.</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4045,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4054,7 +4058,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Order food to where the guest is sitting, or for collection.</t>
+          <t>Track an order to the point it reaches the guest.</t>
         </is>
       </c>
     </row>
@@ -4066,12 +4070,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>Retail / Merchandise</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
@@ -4079,7 +4083,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Track an order to the point it reaches the guest.</t>
+          <t>Find retail / merchandise for this venue.</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4095,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Retail / Merchandise</t>
+          <t>Venue Info &amp; Services</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
@@ -4104,7 +4108,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Find retail / merchandise for this venue.</t>
+          <t>See venue info &amp; services for this venue.</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4120,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Venue Info &amp; Services</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
@@ -4129,7 +4133,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>See venue info &amp; services for this venue.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4145,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>AI Concierge – Chat</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4154,7 +4158,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Work with in-venue notifications for this venue.</t>
+          <t>Add ai concierge – chat for this venue.</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>AI Concierge – Contextual Help</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4179,7 +4183,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4191,12 +4195,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Chat</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
@@ -4204,7 +4208,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Add ai concierge – chat for this venue.</t>
+          <t>See lost &amp; found for this venue.</t>
         </is>
       </c>
     </row>
@@ -4216,12 +4220,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Contextual Help</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
@@ -4229,7 +4233,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Your points, your tier, and what is within reach.</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4245,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
@@ -4254,7 +4258,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>See lost &amp; found for this venue.</t>
+          <t>Find offers &amp; promotions for this venue.</t>
         </is>
       </c>
     </row>
@@ -4266,12 +4270,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>Help &amp; Support</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
@@ -4279,7 +4283,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Your points, your tier, and what is within reach.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4295,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>Multi-Currency &amp; Pricing</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
@@ -4304,7 +4308,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Find offers &amp; promotions for this venue.</t>
+          <t>See prices in your own currency, in the app, before and during the visit.</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4320,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; Support</t>
+          <t>Ticket Delivery &amp; Sharing</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
@@ -4329,7 +4333,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Find ticket delivery &amp; sharing for this venue.</t>
         </is>
       </c>
     </row>
@@ -4341,12 +4345,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Multi-Currency &amp; Pricing</t>
+          <t>Upsell / Cross-Sell</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
@@ -4354,7 +4358,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>See prices in your own currency, in the app, before and during the visit.</t>
+          <t>See upsell / cross-sell for this venue.</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Ticket Delivery &amp; Sharing</t>
+          <t>Interactive Seat Selection</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
@@ -4379,7 +4383,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Find ticket delivery &amp; sharing for this venue.</t>
+          <t>See interactive seat selection for this venue.</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4395,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Upsell / Cross-Sell</t>
+          <t>Bundle Package</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -4404,7 +4408,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>See upsell / cross-sell for this venue.</t>
+          <t>See bundle package for this venue.</t>
         </is>
       </c>
     </row>
@@ -4416,12 +4420,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Interactive Seat Selection</t>
+          <t>Accessibility Information</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
@@ -4429,7 +4433,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>See interactive seat selection for this venue.</t>
+          <t>Step-free routes, facilities and what to expect.</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4445,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Bundle Package</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
@@ -4454,7 +4458,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>See bundle package for this venue.</t>
+          <t>Decide on a dish, choose modifiers, check allergens.</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4470,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Information</t>
+          <t>Privacy &amp; My Data</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
@@ -4479,7 +4483,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Step-free routes, facilities and what to expect.</t>
+          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4495,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>Refunds &amp; Resale</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
@@ -4504,7 +4508,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Decide on a dish, choose modifiers, check allergens.</t>
+          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4520,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Privacy &amp; My Data</t>
+          <t>Help &amp; My Cases</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
@@ -4529,7 +4533,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
+          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4545,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Refunds &amp; Resale</t>
+          <t>Face Pass</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -4554,7 +4558,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
+          <t>🔴 **Biometric enrolment had no guest-facing consent step.** `enrolFacePass` was callable by a guest and reachable from nowhere, which means enrolment was happening at a desk with somebody else operat</t>
         </is>
       </c>
     </row>
@@ -4566,12 +4570,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; My Cases</t>
+          <t>Reserve a Table</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
@@ -4579,7 +4583,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
+          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas are booked by staff (decided 28 September, audit R073 (c)). No deposit and no no-show fee (audit R077 (a)).</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4595,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Face Pass</t>
+          <t>Payment Methods</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -4604,7 +4608,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>🔴 **Biometric enrolment had no guest-facing consent step.** `enrolFacePass` was callable by a guest and reachable from nowhere, which means enrolment was happening at a desk with somebody else operat</t>
+          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4620,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Reserve a Table or Cabana</t>
+          <t>Share &amp; Group Booking</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
@@ -4629,7 +4633,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>**Staff could book a table and a guest could not.** Seven guest-callable operations with no guest surface — reservations, cabanas, and both waitlists.</t>
+          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4645,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Payment Methods</t>
+          <t>Security &amp; Sign-in</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -4654,7 +4658,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
+          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. No second factor: guests have none (decided 28 September, audit R167).</t>
         </is>
       </c>
     </row>
@@ -4666,20 +4670,20 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Share &amp; Group Booking</t>
+          <t>Add to Calendar / Reminders</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
+          <t>Find add to calendar / reminders for this venue.</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Sign-in</t>
+          <t>Saved Items / Wishlist</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -4700,11 +4704,11 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>**A guest could enrol a second factor and not manage it.** Small screen, and it is the one a guest reaches after losing a phone.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4720,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Add to Calendar / Reminders</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Find add to calendar / reminders for this venue.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4745,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Saved Items / Wishlist</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
@@ -4754,7 +4758,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4770,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>Parking – Reservation Confirmed</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -4779,7 +4783,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -4791,12 +4795,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>Feedback &amp; Ratings</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
@@ -4804,7 +4808,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>Work with feedback &amp; ratings for this venue.</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4820,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reservation Confirmed</t>
+          <t>Digital Companion Mode</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -4829,7 +4833,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>The in-venue home: your tickets, the map, and what is near you.</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4845,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Feedback &amp; Ratings</t>
+          <t>Resource Booking – Cabana</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
@@ -4854,7 +4858,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Work with feedback &amp; ratings for this venue.</t>
+          <t>Book a cabana or other capacity-based resource.</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4870,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Digital Companion Mode</t>
+          <t>Resource Availability (Cabana)</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
@@ -4879,7 +4883,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>The in-venue home: your tickets, the map, and what is near you.</t>
+          <t>See which cabanas are free, by area and date, before choosing one.</t>
         </is>
       </c>
     </row>
@@ -4891,12 +4895,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Resource Booking – Cabana</t>
+          <t>Shop &amp; Drop Collection</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
@@ -4904,7 +4908,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Book a cabana or other capacity-based resource.</t>
+          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
         </is>
       </c>
     </row>
@@ -4916,12 +4920,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Plan Your Adventure – Start</t>
+          <t>Newsletter &amp; Preferences</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
@@ -4929,182 +4933,182 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Start a plan for the visit — which attractions, in what order — before arriving.</t>
+          <t>What we may send you, and how.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>White Labelling</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Suggested Itineraries</t>
+          <t>White-Label Branding Management</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Curated plans a guest can take rather than build.</t>
+          <t>See white-label branding management for this venue.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>White Labelling</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Build Your Own Itinerary</t>
+          <t>Domain &amp; Certificate Management</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Choose the attractions and the order yourself.</t>
+          <t>See domain &amp; certificate management for this venue.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>White Labelling</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>AI Optimized Itinerary</t>
+          <t>Localisation &amp; Language Pack</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Let the assistant order the day around waits and opening times.</t>
+          <t>Configure localisation &amp; language pack for this venue.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>White Labelling</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Resource Availability (Cabana)</t>
+          <t>Tenant Workspace</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>See which cabanas are free, by area and date, before choosing one.</t>
+          <t>Land a tenant somewhere that shows what is live and what is not.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>White Labelling</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Plan My Day – In Progress</t>
+          <t>Brand Kit</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>The plan while you are in the venue, against live waits.</t>
+          <t>Set the things every surface reads.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>White Labelling</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Shop &amp; Drop Collection</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
+          <t>Choose the two typefaces and the scale under them.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>White Labelling</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Newsletter &amp; Preferences</t>
+          <t>Logo &amp; Assets</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>What we may send you, and how.</t>
+          <t>Hold the marks every surface needs, at the sizes it needs them.</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5120,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>White-Label Branding Management</t>
+          <t>Theme Editor</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
@@ -5129,7 +5133,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>See white-label branding management for this venue.</t>
+          <t>Tune the theme and watch it apply everywhere at once.</t>
         </is>
       </c>
     </row>
@@ -5141,12 +5145,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate Management</t>
+          <t>Component Preview</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
@@ -5154,7 +5158,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>See domain &amp; certificate management for this venue.</t>
+          <t>Check the theme against the components that carry it.</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5170,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Localisation &amp; Language Pack</t>
+          <t>Page Builder</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
@@ -5179,7 +5183,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Configure localisation &amp; language pack for this venue.</t>
+          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5195,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Tenant Workspace</t>
+          <t>Content Blocks</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -5204,7 +5208,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Land a tenant somewhere that shows what is live and what is not.</t>
+          <t>Define what a block can and cannot contain.</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5220,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Brand Kit</t>
+          <t>Navigation &amp; Menus</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -5229,7 +5233,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Set the things every surface reads.</t>
+          <t>Decide what appears in the header and the footer.</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5245,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Media Library</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -5254,7 +5258,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Choose the two typefaces and the scale under them.</t>
+          <t>Hold the imagery, and know where it is used.</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5270,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Logo &amp; Assets</t>
+          <t>Translations</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -5279,7 +5283,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Hold the marks every surface needs, at the sizes it needs them.</t>
+          <t>Fill in what every language is missing.</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5295,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Theme Editor</t>
+          <t>RTL Preview</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -5304,7 +5308,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Tune the theme and watch it apply everywhere at once.</t>
+          <t>See the site as an Arabic reader sees it.</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5320,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Component Preview</t>
+          <t>SEO &amp; Metadata</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -5329,7 +5333,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Check the theme against the components that carry it.</t>
+          <t>Control how a page looks everywhere it is not the page.</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5345,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Page Builder</t>
+          <t>Publishing Workflow</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -5354,7 +5358,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
+          <t>Move a change from draft to live, with someone accountable.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5370,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Content Blocks</t>
+          <t>Version History</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -5379,7 +5383,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Define what a block can and cannot contain.</t>
+          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5395,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Navigation &amp; Menus</t>
+          <t>Site Settings</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -5404,7 +5408,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Decide what appears in the header and the footer.</t>
+          <t>The values the whole site inherits from.</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5420,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Media Library</t>
+          <t>Domain &amp; Certificate</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -5429,7 +5433,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Hold the imagery, and know where it is used.</t>
+          <t>Point the tenant’s own domain at their site.</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5445,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Translations</t>
+          <t>Consent &amp; Legal</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -5454,7 +5458,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Fill in what every language is missing.</t>
+          <t>Manage the notices every consent is captured against.</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5470,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>RTL Preview</t>
+          <t>User Access</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -5479,212 +5483,12 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>See the site as an Arabic reader sees it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>SEO &amp; Metadata</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>Control how a page looks everywhere it is not the page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>Publishing Workflow</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>Move a change from draft to live, with someone accountable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>Version History</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>See what changed and go back if it was wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>Site Settings</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>The values the whole site inherits from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>Domain &amp; Certificate</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>Point the tenant’s own domain at their site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>Consent &amp; Legal</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Manage the notices every consent is captured against.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>User Access</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
           <t>Say who in the tenant may change what.</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>White Labelling</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>Change Log</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>White Label</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>See who changed what, before the publish that carried it.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E181"/>
+  <autoFilter ref="A1:E173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Platforms'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Services'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,20 +504,20 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>21</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service, Booking &amp; Selection, Cart &amp; Checkout, Discovery &amp; Browse, Engagement &amp; Support, High-Demand Access, In-venue Services, Membership, Loyalty &amp; Value, Promotions, Retail, Support, System States, Ticketing</t>
+          <t>Account &amp; Self-Service, Booking &amp; Selection, Cart &amp; Checkout, Discovery &amp; Browse, Engagement &amp; Support, High-Demand Access, In-venue Services, Membership, Loyalty &amp; Value, Promotions, Retail, Support, System States, Ticketing, Transport</t>
         </is>
       </c>
     </row>
@@ -528,20 +528,20 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>20</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service, Booking &amp; Selection, Cart &amp; Checkout, Discovery, Discovery &amp; Browse, Engagement &amp; Support, High-Demand Access, In-Venue Experience, In-venue Services, Marketing, Membership, Loyalty &amp; Value, Promotions, Retail, Support, System States, Ticketing</t>
+          <t>Account &amp; Self-Service, Booking &amp; Selection, Cart &amp; Checkout, Discovery, Discovery &amp; Browse, Engagement &amp; Support, High-Demand Access, In-Venue Experience, In-venue Services, Marketing, Membership, Loyalty &amp; Value, Promotions, Retail, Support, System States, Ticketing, Transport</t>
         </is>
       </c>
     </row>
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
@@ -686,7 +686,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -756,7 +760,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1150,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2483,7 +2491,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the site, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO and no second factor at sign-in for guests** (decided 28 September, audit R167).</t>
+          <t>Get a guest into the site, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
         </is>
       </c>
     </row>
@@ -3220,20 +3228,20 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Wishlist</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>Queue calls, order updates, venue notices.</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3253,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Devices, Wishlist &amp; Consent</t>
+          <t>Wishlist</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
@@ -3258,7 +3266,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>See loyalty &amp; rewards for this venue.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3278,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Survey &amp; Feedback</t>
+          <t>Devices, Wishlist &amp; Consent</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
@@ -3283,7 +3291,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Work with survey &amp; feedback for this venue.</t>
+          <t>See loyalty &amp; rewards for this venue.</t>
         </is>
       </c>
     </row>
@@ -3295,12 +3303,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Survey &amp; Feedback</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
@@ -3308,107 +3316,107 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Report something you left behind.</t>
+          <t>Work with survey &amp; feedback for this venue.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>Guest App - Web</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Home – Default</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Report something you left behind.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>Guest App - Web</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Explore Categories</t>
+          <t>Map Booking — Cabanas &amp; Spots</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Find explore categories for this venue.</t>
+          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>Guest App - Web</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Event &amp; Attraction Listing</t>
+          <t>Book a Space by the Hour</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>Guest App - Web</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Attraction Details</t>
+          <t>Transport — Route &amp; Schedule</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>See attraction details for this venue.</t>
+          <t>Find a departure between two stations and buy a trip, a multi-trip or unlimited pass, or rebook a saved route.</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3428,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>What's On</t>
+          <t>Home – Default</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3433,7 +3441,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Find what's on for this venue.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3453,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Event / Exhibition Details</t>
+          <t>Explore Categories</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3458,7 +3466,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>See event / exhibition details for this venue.</t>
+          <t>Find explore categories for this venue.</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3478,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Select Date &amp; Time</t>
+          <t>Event &amp; Attraction Listing</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
@@ -3483,7 +3491,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>See select date &amp; time for this venue.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -3495,12 +3503,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Tickets &amp; Add-ons</t>
+          <t>Attraction Details</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
@@ -3508,7 +3516,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Find tickets &amp; add-ons for this venue.</t>
+          <t>See attraction details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3520,12 +3528,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Review &amp; Payment</t>
+          <t>What's On</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
@@ -3533,7 +3541,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Check what you are buying and pay for it.</t>
+          <t>Find what's on for this venue.</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3553,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Booking Confirmation</t>
+          <t>Event / Exhibition Details</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
@@ -3558,7 +3566,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>See event / exhibition details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3578,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>My Tickets</t>
+          <t>Select Date &amp; Time</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
@@ -3583,7 +3591,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>Pick a date, then a time that has room; the tickets for it come next.</t>
         </is>
       </c>
     </row>
@@ -3595,12 +3603,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Ticket Details</t>
+          <t>Tickets &amp; Add-ons</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
@@ -3608,7 +3616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Find ticket details for this venue.</t>
+          <t>Choose which tickets and how many, and any add-ons, for the date and time picked.</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3628,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Review &amp; Payment</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
@@ -3633,7 +3641,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>What we hold about a guest, and what they can change.</t>
+          <t>Check what you are buying and pay for it.</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3653,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Checkout Entry</t>
+          <t>Booking Confirmation</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -3658,7 +3666,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3678,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Simple Registration &amp; OTP</t>
+          <t>My Tickets</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3683,7 +3691,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO and no second factor at sign-in for guests** (decided 28 September, audit R167).</t>
+          <t>Find my tickets for this venue.</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3703,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience</t>
+          <t>Ticket Details</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
@@ -3708,7 +3716,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience — the screen a person opens when they need to deal with arabic / rtl experience.</t>
+          <t>Find ticket details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3728,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
@@ -3733,7 +3741,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Find branded queue / waiting room for this venue.</t>
+          <t>What we hold about a guest, and what they can change.</t>
         </is>
       </c>
     </row>
@@ -3745,12 +3753,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Maintenance / Upgrade Page</t>
+          <t>Checkout Entry</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
@@ -3758,7 +3766,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3778,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Dynamic QR Ticket</t>
+          <t>Simple Registration &amp; OTP</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -3783,7 +3791,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Find dynamic qr ticket for this venue.</t>
+          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3803,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Arabic / RTL Experience</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
@@ -3808,7 +3816,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Find something when you do not know what it is called.</t>
+          <t>Arabic / RTL Experience — the screen a person opens when they need to deal with arabic / rtl experience.</t>
         </is>
       </c>
     </row>
@@ -3820,20 +3828,20 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Wallet Overview</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Find branded queue / waiting room for this venue.</t>
         </is>
       </c>
     </row>
@@ -3845,20 +3853,20 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Ticket Transfer</t>
+          <t>Maintenance / Upgrade Page</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Work with ticket transfer for this venue.</t>
+          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
         </is>
       </c>
     </row>
@@ -3870,20 +3878,20 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Memberships</t>
+          <t>Dynamic QR Ticket</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Find memberships for this venue.</t>
+          <t>Find dynamic qr ticket for this venue.</t>
         </is>
       </c>
     </row>
@@ -3895,20 +3903,20 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Find my reservations for this venue.</t>
+          <t>Find something when you do not know what it is called.</t>
         </is>
       </c>
     </row>
@@ -3920,12 +3928,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Reservation Details</t>
+          <t>Wallet Overview</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
@@ -3933,7 +3941,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>See reservation details for this venue.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3953,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Order History</t>
+          <t>Ticket Transfer</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
@@ -3958,7 +3966,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Find order history (wallet) for this venue.</t>
+          <t>Work with ticket transfer for this venue.</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3978,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Interactive Map</t>
+          <t>Memberships</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
@@ -3983,7 +3991,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>See where things are in relation to each other.</t>
+          <t>Find memberships for this venue.</t>
         </is>
       </c>
     </row>
@@ -3995,12 +4003,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Attraction Wait Times</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
@@ -4008,7 +4016,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>See attraction wait times for this venue.</t>
+          <t>Find my reservations for this venue.</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4028,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>Reservation Details</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
@@ -4033,7 +4041,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Order food to where the guest is sitting, or for collection.</t>
+          <t>See reservation details for this venue.</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4053,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>Order History</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
@@ -4058,7 +4066,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Track an order to the point it reaches the guest.</t>
+          <t>Find order history (wallet) for this venue.</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4078,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Retail / Merchandise</t>
+          <t>Interactive Map</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
@@ -4083,7 +4091,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Find retail / merchandise for this venue.</t>
+          <t>See where things are in relation to each other.</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4103,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Venue Info &amp; Services</t>
+          <t>Attraction Wait Times</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4108,7 +4116,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>See venue info &amp; services for this venue.</t>
+          <t>See attraction wait times for this venue.</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4128,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
@@ -4133,7 +4141,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Order food to where the guest is sitting, or for collection.</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4153,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Chat</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
@@ -4158,7 +4166,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Add ai concierge – chat for this venue.</t>
+          <t>Track an order to the point it reaches the guest.</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4178,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Contextual Help</t>
+          <t>Retail / Merchandise</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
@@ -4183,7 +4191,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Find retail / merchandise for this venue.</t>
         </is>
       </c>
     </row>
@@ -4195,12 +4203,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Venue Info &amp; Services</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
@@ -4208,7 +4216,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>See lost &amp; found for this venue.</t>
+          <t>See venue info &amp; services for this venue.</t>
         </is>
       </c>
     </row>
@@ -4220,12 +4228,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
@@ -4233,7 +4241,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Your points, your tier, and what is within reach.</t>
+          <t>Work with in-venue notifications for this venue.</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4253,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
@@ -4258,7 +4266,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Find offers &amp; promotions for this venue.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4278,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; Support</t>
+          <t>AI Concierge – Chat</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -4283,7 +4291,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Add ai concierge – chat for this venue.</t>
         </is>
       </c>
     </row>
@@ -4295,12 +4303,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Multi-Currency &amp; Pricing</t>
+          <t>AI Concierge – Contextual Help</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
@@ -4308,7 +4316,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>See prices in your own currency, in the app, before and during the visit.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4328,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Ticket Delivery &amp; Sharing</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
@@ -4333,7 +4341,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Find ticket delivery &amp; sharing for this venue.</t>
+          <t>See lost &amp; found for this venue.</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4353,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Upsell / Cross-Sell</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
@@ -4358,7 +4366,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>See upsell / cross-sell for this venue.</t>
+          <t>Your points, your tier, and what is within reach.</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4378,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Interactive Seat Selection</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
@@ -4383,7 +4391,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>See interactive seat selection for this venue.</t>
+          <t>Find offers &amp; promotions for this venue.</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4403,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Bundle Package</t>
+          <t>Help &amp; Support</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
@@ -4408,7 +4416,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>See bundle package for this venue.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4428,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Information</t>
+          <t>Multi-Currency &amp; Pricing</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
@@ -4433,7 +4441,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Step-free routes, facilities and what to expect.</t>
+          <t>See prices in your own currency, in the app, before and during the visit.</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4453,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>Ticket Delivery &amp; Sharing</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
@@ -4458,7 +4466,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Decide on a dish, choose modifiers, check allergens.</t>
+          <t>Find ticket delivery &amp; sharing for this venue.</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4478,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Privacy &amp; My Data</t>
+          <t>Upsell / Cross-Sell</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
@@ -4483,7 +4491,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
+          <t>See upsell / cross-sell for this venue.</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4503,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Refunds &amp; Resale</t>
+          <t>Interactive Seat Selection</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
@@ -4508,7 +4516,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
+          <t>See interactive seat selection for this venue.</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4528,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; My Cases</t>
+          <t>Bundle Package</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
@@ -4533,7 +4541,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
+          <t>See bundle package for this venue.</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4553,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Face Pass</t>
+          <t>Accessibility Information</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
@@ -4558,7 +4566,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>🔴 **Biometric enrolment had no guest-facing consent step.** `enrolFacePass` was callable by a guest and reachable from nowhere, which means enrolment was happening at a desk with somebody else operat</t>
+          <t>Step-free routes, facilities and what to expect.</t>
         </is>
       </c>
     </row>
@@ -4570,12 +4578,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Reserve a Table</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
@@ -4583,7 +4591,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas are booked by staff (decided 28 September, audit R073 (c)). No deposit and no no-show fee (audit R077 (a)).</t>
+          <t>Decide on a dish, choose modifiers, check allergens.</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4603,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Payment Methods</t>
+          <t>Privacy &amp; My Data</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -4608,7 +4616,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
+          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4628,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Share &amp; Group Booking</t>
+          <t>Refunds &amp; Resale</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
@@ -4633,7 +4641,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
+          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
         </is>
       </c>
     </row>
@@ -4645,12 +4653,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Sign-in</t>
+          <t>Help &amp; My Cases</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
@@ -4658,7 +4666,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. No second factor: guests have none (decided 28 September, audit R167).</t>
+          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4678,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Add to Calendar / Reminders</t>
+          <t>Face Pass</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -4679,11 +4687,11 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Find add to calendar / reminders for this venue.</t>
+          <t>🔴 **Biometric enrolment had no guest-facing consent step.** `enrolFacePass` was callable by a guest and reachable from nowhere, which means enrolment was happening at a desk with somebody else operat</t>
         </is>
       </c>
     </row>
@@ -4695,20 +4703,20 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Saved Items / Wishlist</t>
+          <t>Reserve a Table</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas, loungers and other spots on a venue map are booked on GST-074 (decided 29 September, rev 3 REV3-15 and GAP-C2, superseding audit R073 (c)). A deposit only where the venue enabled one (rev 3 REV3-8b, superseding audit R077 (a)).</t>
         </is>
       </c>
     </row>
@@ -4720,20 +4728,20 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>Payment Methods</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
         </is>
       </c>
     </row>
@@ -4745,20 +4753,20 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>Share &amp; Group Booking</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
         </is>
       </c>
     </row>
@@ -4770,20 +4778,20 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reservation Confirmed</t>
+          <t>Security &amp; Sign-in</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. Two-step verification where a venue of the tenant enabled it (decided 29 September, rev 3 GAP-B1, per venue).</t>
         </is>
       </c>
     </row>
@@ -4795,12 +4803,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Feedback &amp; Ratings</t>
+          <t>Add to Calendar / Reminders</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
@@ -4808,7 +4816,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Work with feedback &amp; ratings for this venue.</t>
+          <t>Find add to calendar / reminders for this venue.</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4828,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Digital Companion Mode</t>
+          <t>Saved Items / Wishlist</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
@@ -4833,7 +4841,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>The in-venue home: your tickets, the map, and what is near you.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4853,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Resource Booking – Cabana</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
@@ -4858,7 +4866,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Book a cabana or other capacity-based resource.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4878,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Resource Availability (Cabana)</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
@@ -4883,7 +4891,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>See which cabanas are free, by area and date, before choosing one.</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -4895,12 +4903,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Shop &amp; Drop Collection</t>
+          <t>Parking – Reservation Confirmed</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
@@ -4908,7 +4916,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -4920,12 +4928,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Newsletter &amp; Preferences</t>
+          <t>Feedback &amp; Ratings</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
@@ -4933,282 +4941,282 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>What we may send you, and how.</t>
+          <t>Work with feedback &amp; ratings for this venue.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>White-Label Branding Management</t>
+          <t>Digital Companion Mode</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>See white-label branding management for this venue.</t>
+          <t>The in-venue home: your tickets, the map, and what is near you.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate Management</t>
+          <t>Resource Booking – Cabana</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>See domain &amp; certificate management for this venue.</t>
+          <t>Book a cabana or other capacity-based resource.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Localisation &amp; Language Pack</t>
+          <t>Resource Availability (Cabana)</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Configure localisation &amp; language pack for this venue.</t>
+          <t>See which cabanas are free, by area and date, before choosing one.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Tenant Workspace</t>
+          <t>Shop &amp; Drop Collection</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Land a tenant somewhere that shows what is live and what is not.</t>
+          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Brand Kit</t>
+          <t>Newsletter &amp; Preferences</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Set the things every surface reads.</t>
+          <t>What we may send you, and how.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Map Booking — Cabanas &amp; Spots</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Choose the two typefaces and the scale under them.</t>
+          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Logo &amp; Assets</t>
+          <t>Book a Space by the Hour</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Hold the marks every surface needs, at the sizes it needs them.</t>
+          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Theme Editor</t>
+          <t>Intercity Trip — Route &amp; Schedule</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Tune the theme and watch it apply everywhere at once.</t>
+          <t>Find a departure between two stations for a date and a time of day.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Component Preview</t>
+          <t>Intercity Trip — Route &amp; Passengers</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Check the theme against the components that carry it.</t>
+          <t>See the chosen departure's stops and map, add the passengers and buy the trip.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Page Builder</t>
+          <t>Intercity Trip — Multi-trip Passes</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
+          <t>Buy a 5- or 10-trip card or a weekly or monthly unlimited pass for a station pair.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Content Blocks</t>
+          <t>Intercity Trip — Favourite Routes</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Define what a block can and cannot contain.</t>
+          <t>Rebook a saved route in two taps, or remove it.</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5228,12 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Navigation &amp; Menus</t>
+          <t>White-Label Branding Management</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
@@ -5233,7 +5241,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Decide what appears in the header and the footer.</t>
+          <t>See white-label branding management for this venue.</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5253,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Media Library</t>
+          <t>Domain &amp; Certificate Management</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Hold the imagery, and know where it is used.</t>
+          <t>See domain &amp; certificate management for this venue.</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5278,12 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Translations</t>
+          <t>Localisation &amp; Language Pack</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
@@ -5283,7 +5291,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Fill in what every language is missing.</t>
+          <t>Configure localisation &amp; language pack for this venue.</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5303,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>RTL Preview</t>
+          <t>Tenant Workspace</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -5308,7 +5316,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>See the site as an Arabic reader sees it.</t>
+          <t>Land a tenant somewhere that shows what is live and what is not.</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5328,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>SEO &amp; Metadata</t>
+          <t>Brand Kit</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -5333,7 +5341,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Control how a page looks everywhere it is not the page.</t>
+          <t>Set the things every surface reads.</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5353,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Publishing Workflow</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -5358,7 +5366,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Move a change from draft to live, with someone accountable.</t>
+          <t>Choose the two typefaces and the scale under them.</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5378,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Version History</t>
+          <t>Logo &amp; Assets</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -5383,7 +5391,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
+          <t>Hold the marks every surface needs, at the sizes it needs them.</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5403,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Site Settings</t>
+          <t>Theme Editor</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -5408,7 +5416,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>The values the whole site inherits from.</t>
+          <t>Tune the theme and watch it apply everywhere at once.</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5428,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate</t>
+          <t>Component Preview</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -5433,7 +5441,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Point the tenant’s own domain at their site.</t>
+          <t>Check the theme against the components that carry it.</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5453,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Consent &amp; Legal</t>
+          <t>Page Builder</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -5458,7 +5466,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Manage the notices every consent is captured against.</t>
+          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
         </is>
       </c>
     </row>
@@ -5470,25 +5478,325 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
+          <t>Content Blocks</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Define what a block can and cannot contain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Navigation &amp; Menus</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Decide what appears in the header and the footer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Media Library</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Hold the imagery, and know where it is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Fill in what every language is missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>RTL Preview</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>See the site as an Arabic reader sees it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>SEO &amp; Metadata</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Control how a page looks everywhere it is not the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Publishing Workflow</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Move a change from draft to live, with someone accountable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Version History</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Site Settings</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>The values the whole site inherits from, and the booking-flow settings each venue may override (decided 29 September, rev 3 CFG-11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Domain &amp; Certificate</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Point the tenant’s own domain at their site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Consent &amp; Legal</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Manage the notices every consent is captured against, and the booking consent questions a venue asks ("Are you able to swim?", "I accept the risk"), with the record of every answer (decided 29 September, rev 3 REV3-26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
           <t>User Access</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>White Label</t>
         </is>
       </c>
-      <c r="D173" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="D184" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Say who in the tenant may change what.</t>
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Help Me Choose</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Set up a venue's Help me choose, review what the assistant suggests from the venue's products, preview it and publish it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E173"/>
+  <autoFilter ref="A1:E185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -629,17 +629,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sign-in and people</t>
+          <t>Organisation and settings</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Staff and guest accounts, sign-in, roles and permissions, and personal-data requests.</t>
+          <t>Your organisation, regions, venues, outlets and tills, and the settings each one uses.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nobody can sign in, so everything stops.</t>
+          <t>Nothing can find its venue or settings, so everything stops.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -647,16 +647,8 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>yes</t>
@@ -666,17 +658,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Organisation and settings</t>
+          <t>Sign-in and people</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Your organisation, regions, venues, outlets and tills, and the settings each one uses.</t>
+          <t>Staff and guest accounts, sign-in, roles and permissions, and personal-data requests.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nothing can find its venue or settings, so everything stops.</t>
+          <t>Nobody can sign in, so everything stops.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -684,8 +676,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>yes</t>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -868,17 +868,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Stock levels, counting and purchasing.</t>
+          <t>Menus, table service, kitchen screens and food orders.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Receiving and counting pause; selling continues.</t>
+          <t>Kitchens fall back to printed tickets.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -886,24 +886,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Menus, table service, kitchen screens and food orders.</t>
+          <t>Stock levels, counting and purchasing.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kitchens fall back to printed tickets.</t>
+          <t>Receiving and counting pause; selling continues.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -911,21 +923,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -1061,7 +1061,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Platforms'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Services'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>21</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>35</v>
@@ -552,9 +552,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="D5" s="2" t="n">
         <v>23</v>
       </c>
@@ -802,17 +804,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Wallets and credit</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The financial record of every sale, refund and payment, and currency rates.</t>
+          <t>Guest wallets, stored credit, gift cards and membership credit.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Finance postings wait until it returns; trading is not affected.</t>
+          <t>Wallet balances cannot be spent until it returns.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -835,17 +837,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Wallets and credit</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Guest wallets, stored credit, gift cards and membership credit.</t>
+          <t>The financial record of every sale, refund and payment, and currency rates.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Wallet balances cannot be spent until it returns.</t>
+          <t>Finance postings wait until it returns; trading is not affected.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -868,17 +870,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Venue operations</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Menus, table service, kitchen screens and food orders.</t>
+          <t>Queues and wait times, maintenance, bookable resources, the venue map and media.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Kitchens fall back to printed tickets.</t>
+          <t>Venue operations degrade; selling and entry continue.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -905,17 +907,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Stock levels, counting and purchasing.</t>
+          <t>Menus, table service, kitchen screens and food orders.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Receiving and counting pause; selling continues.</t>
+          <t>Kitchens fall back to printed tickets.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -923,24 +925,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Venue operations</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Queues and wait times, maintenance, bookable resources, the venue map and media.</t>
+          <t>Stock levels, counting and purchasing.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Venue operations degrade; selling and entry continue.</t>
+          <t>Receiving and counting pause; selling continues.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -948,21 +962,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1162,7 +1164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2732,20 +2734,20 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Interactive Seat Selection</t>
+          <t>Plan Your Visit</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Choose specific seats.</t>
+          <t>Plan a visit on the website: answer six questions, get a day-by-day plan, edit it, and book it in one go.</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2759,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Add-ons &amp; Upsell</t>
+          <t>Interactive Seat Selection</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2770,7 +2772,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>See add-ons &amp; upsell for this venue.</t>
+          <t>Choose specific seats.</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2784,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Add-ons &amp; Upsell</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -2795,7 +2797,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Virtual Waiting Room — the screen a person opens when they need to deal with virtual waiting room.</t>
+          <t>See add-ons &amp; upsell for this venue.</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2809,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Wallet &amp; Gift Cards</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -2820,7 +2822,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>See wallet &amp; gift cards for this venue.</t>
+          <t>Virtual Waiting Room — the screen a person opens when they need to deal with virtual waiting room.</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2834,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Membership Plans</t>
+          <t>Wallet &amp; Gift Cards</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2845,7 +2847,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Membership Plans — the screen a person opens when they need to deal with membership plans.</t>
+          <t>See wallet &amp; gift cards for this venue.</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2859,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Membership Management</t>
+          <t>Membership Plans</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2870,7 +2872,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Work with membership management for this venue.</t>
+          <t>Membership Plans — the screen a person opens when they need to deal with membership plans.</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2884,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Newsletter Subscription</t>
+          <t>Membership Management</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
@@ -2895,7 +2897,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Record newsletter subscription for this venue.</t>
+          <t>Work with membership management for this venue.</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2909,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Newsletter Subscription</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
@@ -2920,7 +2922,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>What you have booked and not yet paid for.</t>
+          <t>Record newsletter subscription for this venue.</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2934,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -2945,7 +2947,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>What is on, and what applies to you.</t>
+          <t>What you have booked and not yet paid for.</t>
         </is>
       </c>
     </row>
@@ -2957,12 +2959,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
@@ -2970,7 +2972,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Merchandise, browsable before you arrive.</t>
+          <t>What is on, and what applies to you.</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2984,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -2995,7 +2997,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Order food from a table, a lounger or a seat.</t>
+          <t>Merchandise, browsable before you arrive.</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3009,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3020,7 +3022,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>What is in it, and what may be changed.</t>
+          <t>Order food from a table, a lounger or a seat.</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3034,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3045,7 +3047,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Watch it being made, and settle the bill.</t>
+          <t>What is in it, and what may be changed.</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3059,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Venue Map &amp; Wait Times</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3070,7 +3072,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Where things are, and how long they take.</t>
+          <t>Watch it being made, and settle the bill.</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3084,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>Venue Map &amp; Wait Times</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3095,7 +3097,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Hold a place without standing in one.</t>
+          <t>Where things are, and how long they take.</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3109,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3120,7 +3122,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Reserve a facility before arriving.</t>
+          <t>Hold a place without standing in one.</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3134,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Retail &amp; Shop and Drop</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
@@ -3145,7 +3147,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Buy merchandise and collect it on the way out.</t>
+          <t>Reserve a facility before arriving.</t>
         </is>
       </c>
     </row>
@@ -3157,12 +3159,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>Retail &amp; Shop and Drop</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -3170,7 +3172,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Points, tier, and what the next one needs.</t>
+          <t>Buy merchandise and collect it on the way out.</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3184,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -3195,7 +3197,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Ask, and be answered or handed to a person.</t>
+          <t>Points, tier, and what the next one needs.</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3209,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Help Centre &amp; Accessibility</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
@@ -3220,7 +3222,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Answers, policies and the accessibility statement.</t>
+          <t>Ask, and be answered or handed to a person.</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3234,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>Help Centre &amp; Accessibility</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
@@ -3245,7 +3247,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Queue calls, order updates, venue notices.</t>
+          <t>Answers, policies and the accessibility statement.</t>
         </is>
       </c>
     </row>
@@ -3257,20 +3259,20 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Wishlist</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>Queue calls, order updates, venue notices.</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3284,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Devices, Wishlist &amp; Consent</t>
+          <t>Wishlist</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
@@ -3295,7 +3297,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>See loyalty &amp; rewards for this venue.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -3307,12 +3309,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Survey &amp; Feedback</t>
+          <t>Devices, Wishlist &amp; Consent</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
@@ -3320,7 +3322,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Work with survey &amp; feedback for this venue.</t>
+          <t>See loyalty &amp; rewards for this venue.</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3334,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Survey &amp; Feedback</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
@@ -3345,7 +3347,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Report something you left behind.</t>
+          <t>Work with survey &amp; feedback for this venue.</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3359,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Map Booking — Cabanas &amp; Spots</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
@@ -3370,7 +3372,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
+          <t>Report something you left behind.</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3384,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Book a Space by the Hour</t>
+          <t>Map Booking — Cabanas &amp; Spots</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3395,7 +3397,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
+          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
         </is>
       </c>
     </row>
@@ -3407,12 +3409,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Transport — Route &amp; Schedule</t>
+          <t>Book a Space by the Hour</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
@@ -3420,32 +3422,32 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Find a departure between two stations and buy a trip, a multi-trip or unlimited pass, or rebook a saved route.</t>
+          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>Guest App - Web</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Home – Default</t>
+          <t>Transport — Route &amp; Schedule</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Find a departure between two stations and buy a trip, a multi-trip or unlimited pass, or rebook a saved route.</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3459,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Explore Categories</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3470,7 +3472,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Find explore categories for this venue.</t>
+          <t>The Home tab: what this venue is, when it is open and what there is to do, with one or two highlights per type, from which everything else is entered.</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3484,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Event &amp; Attraction Listing</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3495,7 +3497,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>The Explore tab: search the venue, browse its categories and preview items before opening one.</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3509,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Attraction Details</t>
+          <t>Buy Tickets</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3520,7 +3522,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>See attraction details for this venue.</t>
+          <t>Every bookable product and booking flow of the venue, one tap from any screen.</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3534,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>What's On</t>
+          <t>Item Detail</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3545,7 +3547,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Find what's on for this venue.</t>
+          <t>One detail screen for a ride, show, restaurant or shop: what it is, where it is on the map, and the product to buy for it.</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3559,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Event / Exhibition Details</t>
+          <t>What's On</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3570,7 +3572,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>See event / exhibition details for this venue.</t>
+          <t>Find what's on for this venue.</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3584,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Select Date &amp; Time</t>
+          <t>Item Detail – Event / Exhibition</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
@@ -3595,7 +3597,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Pick a date, then a time that has room; the tickets for it come next.</t>
+          <t>See event / exhibition details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3609,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Tickets &amp; Add-ons</t>
+          <t>Select Date &amp; Time</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3620,7 +3622,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Choose which tickets and how many, and any add-ons, for the date and time picked.</t>
+          <t>Pick a date, then a time that has room; the tickets for it come next.</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3634,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Review &amp; Payment</t>
+          <t>Tickets &amp; Add-ons</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
@@ -3645,7 +3647,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Check what you are buying and pay for it.</t>
+          <t>Choose which tickets and how many, and any add-ons, for the date and time picked.</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3659,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Booking Confirmation</t>
+          <t>Review &amp; Payment</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -3670,7 +3672,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>Check what you are buying and pay for it.</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3684,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>My Tickets</t>
+          <t>Booking Confirmation</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
@@ -3695,7 +3697,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3709,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Ticket Details</t>
+          <t>My Tickets</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3720,7 +3722,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Find ticket details for this venue.</t>
+          <t>Find my tickets for this venue.</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3734,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Ticket Details</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -3745,7 +3747,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>What we hold about a guest, and what they can change.</t>
+          <t>Find ticket details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3759,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Checkout Entry</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
@@ -3770,7 +3772,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>What we hold about a guest, and what they can change.</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3784,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Simple Registration &amp; OTP</t>
+          <t>Checkout Entry</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
@@ -3795,7 +3797,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3809,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience</t>
+          <t>Simple Registration &amp; OTP</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
@@ -3820,7 +3822,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience — the screen a person opens when they need to deal with arabic / rtl experience.</t>
+          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
         </is>
       </c>
     </row>
@@ -3832,12 +3834,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Arabic / RTL Experience</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
@@ -3845,7 +3847,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Find branded queue / waiting room for this venue.</t>
+          <t>Arabic / RTL Experience — the screen a person opens when they need to deal with arabic / rtl experience.</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3859,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Maintenance / Upgrade Page</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
@@ -3870,7 +3872,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
+          <t>Find branded queue / waiting room for this venue.</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3884,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Dynamic QR Ticket</t>
+          <t>Maintenance / Upgrade Page</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
@@ -3895,7 +3897,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Find dynamic qr ticket for this venue.</t>
+          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3909,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
@@ -3920,7 +3922,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Find something when you do not know what it is called.</t>
+          <t>The Plan tab: tell the venue who is coming, when, at what pace and what you like, and get a day-by-day plan.</t>
         </is>
       </c>
     </row>
@@ -3932,20 +3934,20 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Wallet Overview</t>
+          <t>Suggested Itineraries</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Ready-made day plans for this venue that a guest can take instead of answering questions.</t>
         </is>
       </c>
     </row>
@@ -3957,20 +3959,20 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Ticket Transfer</t>
+          <t>Your Plan</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Work with ticket transfer for this venue.</t>
+          <t>The plan, day by day: swap, remove or add items, undo, add Fast Track, then book the whole plan.</t>
         </is>
       </c>
     </row>
@@ -3982,20 +3984,20 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Memberships</t>
+          <t>AI Planner</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Find memberships for this venue.</t>
+          <t>Ask the planner in your own words to change the plan; it refines the rules plan, and the rules plan stays if AI is unavailable.</t>
         </is>
       </c>
     </row>
@@ -4007,20 +4009,20 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Dynamic QR Ticket</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Find my reservations for this venue.</t>
+          <t>Find dynamic qr ticket for this venue.</t>
         </is>
       </c>
     </row>
@@ -4032,20 +4034,20 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Reservation Details</t>
+          <t>Plan in Progress</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>See reservation details for this venue.</t>
+          <t>Today's plan while you are in the venue, re-ordered against live waits.</t>
         </is>
       </c>
     </row>
@@ -4057,20 +4059,20 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Order History</t>
+          <t>Explore – Search Results</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Find order history (wallet) for this venue.</t>
+          <t>Find something when you do not know what it is called.</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4084,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Interactive Map</t>
+          <t>Wallet Overview</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
@@ -4095,7 +4097,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>See where things are in relation to each other.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -4107,12 +4109,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Attraction Wait Times</t>
+          <t>Ticket Transfer</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
@@ -4120,7 +4122,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>See attraction wait times for this venue.</t>
+          <t>Work with ticket transfer for this venue.</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4134,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>Memberships</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
@@ -4145,7 +4147,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Order food to where the guest is sitting, or for collection.</t>
+          <t>Find memberships for this venue.</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4159,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
@@ -4170,7 +4172,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Track an order to the point it reaches the guest.</t>
+          <t>Find my reservations for this venue.</t>
         </is>
       </c>
     </row>
@@ -4182,12 +4184,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Retail / Merchandise</t>
+          <t>Reservation Details</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
@@ -4195,7 +4197,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Find retail / merchandise for this venue.</t>
+          <t>See reservation details for this venue.</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4209,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Venue Info &amp; Services</t>
+          <t>Order History</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
@@ -4220,7 +4222,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>See venue info &amp; services for this venue.</t>
+          <t>Find order history (wallet) for this venue.</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4234,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>Interactive Map</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
@@ -4245,7 +4247,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Work with in-venue notifications for this venue.</t>
+          <t>See where things are in relation to each other.</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4259,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>Attraction Wait Times</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
@@ -4270,7 +4272,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>See attraction wait times for this venue.</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4284,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Chat</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
@@ -4295,7 +4297,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Add ai concierge – chat for this venue.</t>
+          <t>Order food to where the guest is sitting, or for collection.</t>
         </is>
       </c>
     </row>
@@ -4307,12 +4309,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Contextual Help</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
@@ -4320,7 +4322,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Track an order to the point it reaches the guest.</t>
         </is>
       </c>
     </row>
@@ -4332,12 +4334,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Retail / Merchandise</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
@@ -4345,7 +4347,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>See lost &amp; found for this venue.</t>
+          <t>Find retail / merchandise for this venue.</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4359,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>Venue Info &amp; Services</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
@@ -4370,7 +4372,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Your points, your tier, and what is within reach.</t>
+          <t>See venue info &amp; services for this venue.</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4384,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
@@ -4395,7 +4397,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Find offers &amp; promotions for this venue.</t>
+          <t>Work with in-venue notifications for this venue.</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4409,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; Support</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -4420,7 +4422,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
         </is>
       </c>
     </row>
@@ -4432,12 +4434,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Multi-Currency &amp; Pricing</t>
+          <t>AI Concierge – Chat</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
@@ -4445,7 +4447,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>See prices in your own currency, in the app, before and during the visit.</t>
+          <t>Add ai concierge – chat for this venue.</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4459,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Ticket Delivery &amp; Sharing</t>
+          <t>AI Concierge – Contextual Help</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
@@ -4470,7 +4472,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Find ticket delivery &amp; sharing for this venue.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4484,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Upsell / Cross-Sell</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
@@ -4495,7 +4497,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>See upsell / cross-sell for this venue.</t>
+          <t>See lost &amp; found for this venue.</t>
         </is>
       </c>
     </row>
@@ -4507,12 +4509,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Interactive Seat Selection</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
@@ -4520,7 +4522,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>See interactive seat selection for this venue.</t>
+          <t>Your points, your tier, and what is within reach.</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4534,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Bundle Package</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
@@ -4545,7 +4547,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>See bundle package for this venue.</t>
+          <t>Find offers &amp; promotions for this venue.</t>
         </is>
       </c>
     </row>
@@ -4557,12 +4559,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Information</t>
+          <t>Help &amp; Support</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
@@ -4570,7 +4572,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Step-free routes, facilities and what to expect.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4584,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>Multi-Currency &amp; Pricing</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
@@ -4595,7 +4597,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Decide on a dish, choose modifiers, check allergens.</t>
+          <t>See prices in your own currency, in the app, before and during the visit.</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4609,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Privacy &amp; My Data</t>
+          <t>Ticket Delivery &amp; Sharing</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -4620,7 +4622,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
+          <t>Find ticket delivery &amp; sharing for this venue.</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4634,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Refunds &amp; Resale</t>
+          <t>Upsell / Cross-Sell</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
@@ -4645,7 +4647,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
+          <t>See upsell / cross-sell for this venue.</t>
         </is>
       </c>
     </row>
@@ -4657,12 +4659,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; My Cases</t>
+          <t>Interactive Seat Selection</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
@@ -4670,7 +4672,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
+          <t>See interactive seat selection for this venue.</t>
         </is>
       </c>
     </row>
@@ -4682,12 +4684,12 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Face Pass</t>
+          <t>Bundle Package</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
@@ -4695,7 +4697,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>🔴 **Biometric enrolment had no guest-facing consent step.** `enrolFacePass` was callable by a guest and reachable from nowhere, which means enrolment was happening at a desk with somebody else operat</t>
+          <t>See bundle package for this venue.</t>
         </is>
       </c>
     </row>
@@ -4707,12 +4709,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Reserve a Table</t>
+          <t>Accessibility Information</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
@@ -4720,7 +4722,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas, loungers and other spots on a venue map are booked on GST-074 (decided 29 September, rev 3 REV3-15 and GAP-C2, superseding audit R073 (c)). A deposit only where the venue enabled one (rev 3 REV3-8b, superseding audit R077 (a)).</t>
+          <t>Step-free routes, facilities and what to expect.</t>
         </is>
       </c>
     </row>
@@ -4732,12 +4734,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Payment Methods</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
@@ -4745,7 +4747,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
+          <t>Decide on a dish, choose modifiers, check allergens.</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4759,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Share &amp; Group Booking</t>
+          <t>Privacy &amp; My Data</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
@@ -4770,7 +4772,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
+          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4784,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Sign-in</t>
+          <t>Refunds &amp; Resale</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -4795,7 +4797,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. Two-step verification where a venue of the tenant enabled it (decided 29 September, rev 3 GAP-B1, per venue).</t>
+          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
         </is>
       </c>
     </row>
@@ -4807,20 +4809,20 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Add to Calendar / Reminders</t>
+          <t>Help &amp; My Cases</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Find add to calendar / reminders for this venue.</t>
+          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4834,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Saved Items / Wishlist</t>
+          <t>Face Pass</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -4841,11 +4843,11 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>🔴 **Biometric enrolment had no guest-facing consent step.** `enrolFacePass` was callable by a guest and reachable from nowhere, which means enrolment was happening at a desk with somebody else operat</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4859,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>Reserve a Table</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -4866,11 +4868,11 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas, loungers and other spots on a venue map are booked on GST-074 (decided 29 September, rev 3 REV3-15 and GAP-C2, superseding audit R073 (c)). A deposit only where the venue enabled one (rev 3 REV3-8b, superseding audit R077 (a)).</t>
         </is>
       </c>
     </row>
@@ -4882,20 +4884,20 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>Payment Methods</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
         </is>
       </c>
     </row>
@@ -4907,20 +4909,20 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reservation Confirmed</t>
+          <t>Share &amp; Group Booking</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
         </is>
       </c>
     </row>
@@ -4932,20 +4934,20 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Feedback &amp; Ratings</t>
+          <t>Security &amp; Sign-in</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Work with feedback &amp; ratings for this venue.</t>
+          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. Two-step verification where a venue of the tenant enabled it (decided 29 September, rev 3 GAP-B1, per venue).</t>
         </is>
       </c>
     </row>
@@ -4957,12 +4959,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Digital Companion Mode</t>
+          <t>Add to Calendar / Reminders</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
@@ -4970,7 +4972,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The in-venue home: your tickets, the map, and what is near you.</t>
+          <t>Find add to calendar / reminders for this venue.</t>
         </is>
       </c>
     </row>
@@ -4982,12 +4984,12 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Resource Booking – Cabana</t>
+          <t>Saved Items / Wishlist</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
@@ -4995,7 +4997,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Book a cabana or other capacity-based resource.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -5007,12 +5009,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Resource Availability (Cabana)</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
@@ -5020,7 +5022,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>See which cabanas are free, by area and date, before choosing one.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5034,12 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Shop &amp; Drop Collection</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
@@ -5045,7 +5047,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5059,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Newsletter &amp; Preferences</t>
+          <t>Parking – Reservation Confirmed</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
@@ -5070,7 +5072,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>What we may send you, and how.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5084,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Map Booking — Cabanas &amp; Spots</t>
+          <t>Feedback &amp; Ratings</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
@@ -5095,7 +5097,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
+          <t>Work with feedback &amp; ratings for this venue.</t>
         </is>
       </c>
     </row>
@@ -5107,12 +5109,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Book a Space by the Hour</t>
+          <t>At the Venue</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
@@ -5120,7 +5122,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
+          <t>Everything live at the venue in one place: map, waits, food, shows, shop and services, with what is happening now.</t>
         </is>
       </c>
     </row>
@@ -5132,12 +5134,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Route &amp; Schedule</t>
+          <t>Resource Booking – Cabana</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
@@ -5145,7 +5147,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Find a departure between two stations for a date and a time of day.</t>
+          <t>Book a cabana or other capacity-based resource.</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5159,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Route &amp; Passengers</t>
+          <t>Resource Availability (Cabana)</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
@@ -5170,7 +5172,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>See the chosen departure's stops and map, add the passengers and buy the trip.</t>
+          <t>See which cabanas are free, by area and date, before choosing one.</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5184,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Multi-trip Passes</t>
+          <t>Shop &amp; Drop Collection</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
@@ -5195,7 +5197,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Buy a 5- or 10-trip card or a weekly or monthly unlimited pass for a station pair.</t>
+          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5209,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Favourite Routes</t>
+          <t>Newsletter &amp; Preferences</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
@@ -5220,157 +5222,157 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Rebook a saved route in two taps, or remove it.</t>
+          <t>What we may send you, and how.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>White-Label Branding Management</t>
+          <t>Map Booking — Cabanas &amp; Spots</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>See white-label branding management for this venue.</t>
+          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate Management</t>
+          <t>Book a Space by the Hour</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>See domain &amp; certificate management for this venue.</t>
+          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Localisation &amp; Language Pack</t>
+          <t>Intercity Trip — Route &amp; Schedule</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Configure localisation &amp; language pack for this venue.</t>
+          <t>Find a departure between two stations for a date and a time of day.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Tenant Workspace</t>
+          <t>Intercity Trip — Route &amp; Passengers</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Land a tenant somewhere that shows what is live and what is not.</t>
+          <t>See the chosen departure's stops and map, add the passengers and buy the trip.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Brand Kit</t>
+          <t>Intercity Trip — Multi-trip Passes</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Set the things every surface reads.</t>
+          <t>Buy a 5- or 10-trip card or a weekly or monthly unlimited pass for a station pair.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Intercity Trip — Favourite Routes</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Choose the two typefaces and the scale under them.</t>
+          <t>Rebook a saved route in two taps, or remove it.</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5384,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Logo &amp; Assets</t>
+          <t>Site Builder</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -5391,11 +5393,11 @@
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Hold the marks every surface needs, at the sizes it needs them.</t>
+          <t>Build a working site in about 30 minutes: pick a preset, then walk seven saved steps (venue and modules, ticketing flows, compose steps, Help me choose, look and feel, mobile app, preview and publish), each opening the full screen for its details. **The preset keeps the minimum path short (M24-05)**: it proposes the modules, the booking flows with their default step order, the home sections and the mobile tabs, so the only things an operator must supply are a logo, four colours and a Publish; everything else keeps the preset or the contract default and can be refined later.</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5409,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Theme Editor</t>
+          <t>Booking Flows</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -5416,11 +5418,11 @@
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Tune the theme and watch it apply everywhere at once.</t>
+          <t>Pick the venue's booking flows, turn optional steps on or off, set the step order within the allowed limits with a live preview, assign flows to products and categories, and validate them before they publish with the site.</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5434,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Component Preview</t>
+          <t>App Build &amp; Store Publishing</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -5441,11 +5443,11 @@
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Check the theme against the components that carry it.</t>
+          <t>Get the tenant's own app into the App Store and Google Play under the client's own accounts — checklist, store listing, request a build, download or submit it, follow its review — with a guide for the steps only the client can take.</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5459,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Page Builder</t>
+          <t>White-Label Branding Management</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
@@ -5470,7 +5472,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
+          <t>See white-label branding management for this venue.</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5484,12 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Content Blocks</t>
+          <t>Domain &amp; Certificate Management</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
@@ -5495,7 +5497,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Define what a block can and cannot contain.</t>
+          <t>See domain &amp; certificate management for this venue.</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5509,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Navigation &amp; Menus</t>
+          <t>Localisation &amp; Language Pack</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
@@ -5520,7 +5522,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Decide what appears in the header and the footer.</t>
+          <t>Configure localisation &amp; language pack for this venue.</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5534,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Media Library</t>
+          <t>Tenant Workspace</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -5545,7 +5547,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Hold the imagery, and know where it is used.</t>
+          <t>Land a tenant somewhere that shows what is live and what is not, and hold step 1 of the Site Builder (venue and modules).</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5559,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Translations</t>
+          <t>Brand Kit</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -5570,7 +5572,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Fill in what every language is missing.</t>
+          <t>Set the things every surface reads.</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5584,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>RTL Preview</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -5595,7 +5597,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>See the site as an Arabic reader sees it.</t>
+          <t>Choose the two typefaces and the scale under them.</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5609,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>SEO &amp; Metadata</t>
+          <t>Logo &amp; Assets</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -5620,7 +5622,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Control how a page looks everywhere it is not the page.</t>
+          <t>Hold the marks every surface needs, at the sizes it needs them, and the mobile app's intro video (Site Builder steps 5 and 6).</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5634,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Publishing Workflow</t>
+          <t>Theme Editor</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -5645,7 +5647,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Move a change from draft to live, with someone accountable.</t>
+          <t>Tune the theme and watch it apply everywhere at once.</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5659,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Version History</t>
+          <t>Component Preview</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -5670,7 +5672,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
+          <t>Check the theme against the components that carry it.</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5684,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Site Settings</t>
+          <t>Page Builder</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -5695,7 +5697,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>The values the whole site inherits from, and the booking-flow settings each venue may override (decided 29 September, rev 3 CFG-11).</t>
+          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5709,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate</t>
+          <t>Content Blocks</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -5720,7 +5722,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Point the tenant’s own domain at their site.</t>
+          <t>Define what a block can and cannot contain, and set the banners (Site Builder step 5).</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5734,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Consent &amp; Legal</t>
+          <t>Navigation &amp; Menus</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -5745,7 +5747,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Manage the notices every consent is captured against, and the booking consent questions a venue asks ("Are you able to swim?", "I accept the risk"), with the record of every answer (decided 29 September, rev 3 REV3-26).</t>
+          <t>Decide what appears in the header, the footer and the mobile tab bar, with the Buy tickets button (Site Builder steps 5 and 6).</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5759,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>User Access</t>
+          <t>Media Library</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -5770,7 +5772,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Say who in the tenant may change what.</t>
+          <t>Hold the imagery, and know where it is used.</t>
         </is>
       </c>
     </row>
@@ -5782,25 +5784,250 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Fill in what every language is missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>RTL Preview</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>See the site as an Arabic reader sees it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>SEO &amp; Metadata</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Control how a page looks everywhere it is not the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Publishing Workflow</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Move a change from draft to live, with someone accountable (Site Builder step 7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Version History</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Site Settings</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>The values the whole site inherits from, and the venue-wide booking settings each venue may override (decided 29 September, rev 3 CFG-11); the settings of one flow are on CMS-103 (W12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Domain &amp; Certificate</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Point the tenant’s own domain at their site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Consent &amp; Legal</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Manage the notices every consent is captured against, and the booking consent questions a venue asks ("Are you able to swim?", "I accept the risk"), with the record of every answer (decided 29 September, rev 3 REV3-26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>User Access</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Say who in the tenant may change what.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
           <t>Help Me Choose</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>White Label</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>Set up a venue's Help me choose, review what the assistant suggests from the venue's products, preview it and publish it.</t>
+      <c r="D194" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Set up a venue's Help me choose so its answers filter the catalogue, review the question set the assistant proposes from the venue's products, preview the filtered list and publish it (Site Builder step 4).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E185"/>
+  <autoFilter ref="A1:E194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -2822,7 +2822,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Virtual Waiting Room — the screen a person opens when they need to deal with virtual waiting room.</t>
+          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Find branded queue / waiting room for this venue.</t>
+          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
         </is>
       </c>
     </row>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Platforms'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Services'!$A$1:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$E$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>13</v>
@@ -534,10 +534,10 @@
         <v>25</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>3</v>
@@ -560,10 +560,12 @@
       <c r="D5" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation, White Label</t>
+          <t>Branding &amp; Localisation, Tenants &amp; Licensing, White Label</t>
         </is>
       </c>
     </row>
@@ -935,11 +937,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1164,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1422,7 +1420,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Returns, Refunds &amp; Exchanges — from the client design board, 20 August.</t>
+          <t>Take back a sale, refund it or exchange it, against the original receipt.</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1470,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Mobile POS, Event Sales &amp; Offline Operations — from the client design board, 20 August.</t>
+          <t>Keep selling while the till is offline, and see what the server refused when it syncs.</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Cash Operations Dashboard — from the client design board, 20 August.</t>
+          <t>See the live cash position of every till, for a supervisor.</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1545,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Till Configuration — from the client design board, 20 August.</t>
+          <t>Configure this till in place: its workstation settings, its peripherals and the cashier's deposit box.</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1595,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Safe Drop &amp; Cash Transfer Management — from the client design board, 20 August.</t>
+          <t>Drop cash from a drawer to the safe when it passes the ceiling.</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1620,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Shift Templates &amp; Policies — from the client design board, 20 August.</t>
+          <t>See this till's shifts and the opening and closing rules they run under.</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1845,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Open, move, merge and close table visits from the floor.</t>
+          <t>Seat parties and close table visits from the floor.</t>
         </is>
       </c>
     </row>
@@ -1884,20 +1882,20 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Operations Command Center</t>
+          <t>Sales Journal</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Operations Command Center — board 3 of the client F&amp;B design set.</t>
+          <t>Find a sale this till made and act on it — reprint or email the receipt, issue a tax invoice, reload it into the cart, or hand it to returns.</t>
         </is>
       </c>
     </row>
@@ -1909,20 +1907,20 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Display System (KDS)</t>
+          <t>Reservations &amp; Group Arrivals</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Display System (KDS) — board 3 of the client F&amp;B design set.</t>
+          <t>Hold a sale without payment, and take payment when the guest or the group arrives.</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1932,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Order Firing &amp; Course Management</t>
+          <t>Kitchen Operations Command Center</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1947,7 +1945,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Order Firing &amp; Course Management — board 3 of the client F&amp;B design set.</t>
+          <t>Kitchen Operations Command Center — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1957,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Active Order Management &amp; Fulfilment Journey</t>
+          <t>Kitchen Display System (KDS)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1972,7 +1970,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Active Order Management &amp; Fulfilment Journey — board 3 of the client F&amp;B design set.</t>
+          <t>Kitchen Display System (KDS) — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1982,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Station Workload &amp; Dynamic Routing</t>
+          <t>Order Firing &amp; Course Management</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1997,7 +1995,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Station Workload &amp; Dynamic Routing — board 3 of the client F&amp;B design set.</t>
+          <t>Order Firing &amp; Course Management — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2007,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Expeditor &amp; Order Assembly</t>
+          <t>Active Order Management &amp; Fulfilment Journey</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2022,7 +2020,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Expeditor &amp; Order Assembly — board 3 of the client F&amp;B design set.</t>
+          <t>Follow one order from the till to the pass and out to the guest.</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2032,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Guest Collection, Buzzer &amp; Digital Notification</t>
+          <t>Kitchen Station Workload &amp; Dynamic Routing</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2047,7 +2045,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Guest Collection, Buzzer &amp; Digital Notification — board 3 of the client F&amp;B design set.</t>
+          <t>Kitchen Station Workload &amp; Dynamic Routing — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Exceptions, Re-Fire &amp; Unavailable Items</t>
+          <t>Expeditor &amp; Order Assembly</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2072,7 +2070,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Exceptions, Re-Fire &amp; Unavailable Items — board 3 of the client F&amp;B design set.</t>
+          <t>Expeditor &amp; Order Assembly — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2082,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SLA, Priority &amp; Service Rules</t>
+          <t>Guest Collection, Buzzer &amp; Digital Notification</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2097,7 +2095,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>SLA, Priority &amp; Service Rules — board 3 of the client F&amp;B design set.</t>
+          <t>Guest Collection, Buzzer &amp; Digital Notification — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2107,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Performance, AI &amp; Operational Optimization</t>
+          <t>Exceptions, Re-Fire &amp; Unavailable Items</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2122,7 +2120,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Performance, AI &amp; Operational Optimization — board 3 of the client F&amp;B design set.</t>
+          <t>Exceptions, Re-Fire &amp; Unavailable Items — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2132,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Sell — Seat Map</t>
+          <t>SLA, Priority &amp; Service Rules</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2147,7 +2145,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Choose specific seats for a seated event.</t>
+          <t>SLA, Priority &amp; Service Rules — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2157,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Kitchen Performance, AI &amp; Operational Optimization</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2172,7 +2170,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>See how the day is going from the terminal.</t>
+          <t>Kitchen Performance, AI &amp; Operational Optimization — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2182,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Staff Roster</t>
+          <t>Sell — Seat Map</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2197,57 +2195,57 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>See who is on duty and on which terminal.</t>
+          <t>Choose specific seats for a seated event.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Web</t>
+          <t>Point of Sale</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Home / Landing</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Show a guest what is on and give them one obvious way to start booking.</t>
+          <t>See how the day is going from the terminal.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Web</t>
+          <t>Point of Sale</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Event &amp; Attraction Listing</t>
+          <t>Staff Roster</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Browse and filter everything bookable.</t>
+          <t>See who is on duty and on which terminal.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2257,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Search Results</t>
+          <t>Home / Landing</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2272,7 +2270,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Find something when the guest does not know what it is called.</t>
+          <t>Show a guest what is on and give them one obvious way to start booking.</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2282,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Attraction Details</t>
+          <t>Event &amp; Attraction Listing</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2297,7 +2295,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Decide whether to book this.</t>
+          <t>Browse and filter everything bookable.</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2307,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Ticket Type Selection</t>
+          <t>Search Results</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -2322,7 +2320,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Choose which ticket and how many.</t>
+          <t>Find something when the guest does not know what it is called.</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2332,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Date &amp; Performance Selection</t>
+          <t>Attraction Details</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2347,7 +2345,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Pick a date and time that has capacity.</t>
+          <t>Decide whether to book this.</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2357,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Shopping Cart</t>
+          <t>Ticket Type Selection</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2372,7 +2370,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Review and confirm what is being bought.</t>
+          <t>Choose which ticket and how many.</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2382,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Guest Details &amp; Attendee Forms</t>
+          <t>Date &amp; Performance Selection</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2397,7 +2395,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Collect who is coming and how to reach them.</t>
+          <t>Pick a date and time that has capacity.</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2407,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Checkout — Payment</t>
+          <t>Shopping Cart</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2422,7 +2420,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Take payment and create the order.</t>
+          <t>Review and confirm what is being bought.</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2432,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Booking Confirmation</t>
+          <t>Guest Details &amp; Attendee Forms</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2447,7 +2445,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Confirm the purchase and deliver the tickets.</t>
+          <t>Collect who is coming and how to reach them.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2457,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Pay for a Booking</t>
+          <t>Checkout — Payment</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2472,7 +2470,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Pay for a booking somebody else took, without an account.</t>
+          <t>Take payment and create the order.</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2482,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Login / Register</t>
+          <t>Booking Confirmation</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2497,7 +2495,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the site, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
+          <t>Confirm the purchase and deliver the tickets.</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2507,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>My Account Dashboard</t>
+          <t>Pay for a Booking</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2522,7 +2520,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Pay for a booking somebody else took, without an account.</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2532,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>My Tickets</t>
+          <t>Login / Register</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2547,7 +2545,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>Get a guest into the site, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2557,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Order History</t>
+          <t>My Account Dashboard</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2572,7 +2570,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Find order history for this venue.</t>
+          <t>Everything I have with this venue at a glance: bookings, wallet, loyalty, challenges and invitations, each opening its own pane.</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2582,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Profile &amp; Preferences</t>
+          <t>My Tickets</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2597,7 +2595,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Change how profile behaves here, and see which level the current value came from.</t>
+          <t>Find my tickets for this venue.</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2607,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Help Centre / FAQ</t>
+          <t>Order History</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -2622,7 +2620,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Find order history for this venue.</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2632,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Contact &amp; Venue Information</t>
+          <t>Profile &amp; Preferences</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -2647,7 +2645,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Find contact &amp; venue information for this venue.</t>
+          <t>Correct your details, choose what we may send you, and record your needs.</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2657,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Error / Sold Out / Maintenance</t>
+          <t>Help Centre / FAQ</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -2672,7 +2670,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2682,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Ticket Transfer</t>
+          <t>Contact &amp; Venue Information</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -2697,7 +2695,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Send a ticket to someone else, and see what you have sent.</t>
+          <t>Find contact &amp; venue information for this venue.</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2707,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Multi-Currency &amp; Pricing</t>
+          <t>Error / Sold Out / Maintenance</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -2722,7 +2720,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Compare prices in your own currency before you travel.</t>
+          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
         </is>
       </c>
     </row>
@@ -2734,12 +2732,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Plan Your Visit</t>
+          <t>Ticket Transfer</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -2747,7 +2745,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Plan a visit on the website: answer six questions, get a day-by-day plan, edit it, and book it in one go.</t>
+          <t>Send a ticket to someone else, and see what you have sent.</t>
         </is>
       </c>
     </row>
@@ -2759,20 +2757,20 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Interactive Seat Selection</t>
+          <t>Multi-Currency &amp; Pricing</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Choose specific seats.</t>
+          <t>Choose the currency you see prices in and pay in.</t>
         </is>
       </c>
     </row>
@@ -2784,20 +2782,20 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Add-ons &amp; Upsell</t>
+          <t>Plan Your Visit</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>See add-ons &amp; upsell for this venue.</t>
+          <t>Plan a visit on the website: answer six questions, get a day-by-day plan, edit it, and book it in one go.</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2807,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Interactive Seat Selection</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -2822,7 +2820,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
+          <t>Choose specific seats.</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2832,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Wallet &amp; Gift Cards</t>
+          <t>Add-ons &amp; Upsell</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -2847,7 +2845,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>See wallet &amp; gift cards for this venue.</t>
+          <t>See add-ons &amp; upsell for this venue.</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2857,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Membership Plans</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
@@ -2872,7 +2870,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Membership Plans — the screen a person opens when they need to deal with membership plans.</t>
+          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2882,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Membership Management</t>
+          <t>Wallet &amp; Gift Cards</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2897,7 +2895,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Work with membership management for this venue.</t>
+          <t>See wallet &amp; gift cards for this venue.</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2907,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Newsletter Subscription</t>
+          <t>Membership Plans</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
@@ -2922,7 +2920,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Record newsletter subscription for this venue.</t>
+          <t>Membership Plans — the screen a person opens when they need to deal with membership plans.</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2932,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Membership Management</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -2947,7 +2945,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>What you have booked and not yet paid for.</t>
+          <t>Work with membership management for this venue.</t>
         </is>
       </c>
     </row>
@@ -2959,12 +2957,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>Newsletter Subscription</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
@@ -2972,7 +2970,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>What is on, and what applies to you.</t>
+          <t>Choose which newsletters you receive and on which channel, or leave one from its email link.</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2982,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -2997,7 +2995,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Merchandise, browsable before you arrive.</t>
+          <t>What you have booked and not yet paid for.</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3007,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3022,7 +3020,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Order food from a table, a lounger or a seat.</t>
+          <t>What is on, and what applies to you.</t>
         </is>
       </c>
     </row>
@@ -3034,12 +3032,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -3047,7 +3045,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>What is in it, and what may be changed.</t>
+          <t>Merchandise, browsable before you arrive.</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3057,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3072,7 +3070,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Watch it being made, and settle the bill.</t>
+          <t>Order food from a table, a lounger or a seat.</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3082,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Venue Map &amp; Wait Times</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3097,7 +3095,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Where things are, and how long they take.</t>
+          <t>What is in it, and what may be changed.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3107,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3122,7 +3120,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Hold a place without standing in one.</t>
+          <t>Watch it being made, and see the table bill; it is paid at the table.</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3132,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>Venue Map &amp; Wait Times</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3147,7 +3145,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Reserve a facility before arriving.</t>
+          <t>Where things are, and how long they take.</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3157,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Retail &amp; Shop and Drop</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -3172,7 +3170,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Buy merchandise and collect it on the way out.</t>
+          <t>Hold a place without standing in one.</t>
         </is>
       </c>
     </row>
@@ -3184,12 +3182,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -3197,7 +3195,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Points, tier, and what the next one needs.</t>
+          <t>Reserve a facility before arriving.</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3207,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>Retail &amp; Shop and Drop</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
@@ -3222,7 +3220,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Ask, and be answered or handed to a person.</t>
+          <t>Buy merchandise and collect it on the way out.</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3232,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Help Centre &amp; Accessibility</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
@@ -3247,7 +3245,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Answers, policies and the accessibility statement.</t>
+          <t>Points, tier, and what the next one needs.</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3257,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3272,7 +3270,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Queue calls, order updates, venue notices.</t>
+          <t>Ask, and be answered or handed to a person.</t>
         </is>
       </c>
     </row>
@@ -3284,20 +3282,20 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Wishlist</t>
+          <t>Help Centre &amp; Accessibility</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>Answers, policies and the accessibility statement.</t>
         </is>
       </c>
     </row>
@@ -3309,20 +3307,20 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Devices, Wishlist &amp; Consent</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>See loyalty &amp; rewards for this venue.</t>
+          <t>Queue calls, order updates, venue notices.</t>
         </is>
       </c>
     </row>
@@ -3334,12 +3332,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Survey &amp; Feedback</t>
+          <t>Wishlist</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
@@ -3347,7 +3345,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Work with survey &amp; feedback for this venue.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3357,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Devices, Wishlist &amp; Consent</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
@@ -3372,7 +3370,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Report something you left behind.</t>
+          <t>Your devices, security, cookie choices and data rights.</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3382,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Map Booking — Cabanas &amp; Spots</t>
+          <t>Survey &amp; Feedback</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
@@ -3397,7 +3395,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
+          <t>Tell the venue how the visit went, answer a survey it sent, or report a problem.</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3407,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Book a Space by the Hour</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
@@ -3422,7 +3420,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
+          <t>Report something you left behind.</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3432,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Transport — Route &amp; Schedule</t>
+          <t>Map Booking — Cabanas &amp; Spots</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
@@ -3447,57 +3445,57 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Find a departure between two stations and buy a trip, a multi-trip or unlimited pass, or rebook a saved route.</t>
+          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>Guest App - Web</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Book a Space by the Hour</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>The Home tab: what this venue is, when it is open and what there is to do, with one or two highlights per type, from which everything else is entered.</t>
+          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Guest App - Mobile</t>
+          <t>Guest App - Web</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Transport — Route &amp; Schedule</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>The Explore tab: search the venue, browse its categories and preview items before opening one.</t>
+          <t>Find a departure between two stations and buy a trip, a multi-trip or unlimited pass, or rebook a saved route.</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3507,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Buy Tickets</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3522,7 +3520,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Every bookable product and booking flow of the venue, one tap from any screen.</t>
+          <t>The Home tab: what this venue is, when it is open and what there is to do, with the highlights per type the venue chose, from which everything else is entered.</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3532,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Item Detail</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3547,7 +3545,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>One detail screen for a ride, show, restaurant or shop: what it is, where it is on the map, and the product to buy for it.</t>
+          <t>The Explore tab: search the venue, browse its categories and preview items before opening one.</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3557,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>What's On</t>
+          <t>Buy Tickets</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3572,7 +3570,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Find what's on for this venue.</t>
+          <t>Every bookable product and booking flow of the venue, one tap from any screen.</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3582,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Item Detail – Event / Exhibition</t>
+          <t>Item Detail</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3597,7 +3595,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>See event / exhibition details for this venue.</t>
+          <t>One detail screen for a ride, show, restaurant or shop: what it is, where it is on the map, and the product to buy for it.</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3607,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Select Date &amp; Time</t>
+          <t>What's On</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
@@ -3622,7 +3620,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Pick a date, then a time that has room; the tickets for it come next.</t>
+          <t>Find what's on for this venue.</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3632,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Tickets &amp; Add-ons</t>
+          <t>Item Detail – Event / Exhibition</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
@@ -3647,7 +3645,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Choose which tickets and how many, and any add-ons, for the date and time picked.</t>
+          <t>See event / exhibition details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3657,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Review &amp; Payment</t>
+          <t>Select Date &amp; Time</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
@@ -3672,7 +3670,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Check what you are buying and pay for it.</t>
+          <t>Pick a date, then a time that has room; the tickets for it come next.</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3682,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Booking Confirmation</t>
+          <t>Tickets &amp; Add-ons</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
@@ -3697,7 +3695,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>Choose which tickets and how many, and any add-ons, for the date and time picked.</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3707,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>My Tickets</t>
+          <t>Review &amp; Payment</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
@@ -3722,7 +3720,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>Check what you are buying and pay for it.</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3732,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Ticket Details</t>
+          <t>Booking Confirmation</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
@@ -3747,7 +3745,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Find ticket details for this venue.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3757,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>My Tickets</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -3772,7 +3770,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>What we hold about a guest, and what they can change.</t>
+          <t>Find my tickets for this venue.</t>
         </is>
       </c>
     </row>
@@ -3784,12 +3782,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Checkout Entry</t>
+          <t>Ticket Details</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
@@ -3797,7 +3795,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>Find ticket details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3807,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Simple Registration &amp; OTP</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -3822,7 +3820,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
+          <t>What we hold about a guest, and what they can change.</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3832,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience</t>
+          <t>Checkout Entry</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
@@ -3847,7 +3845,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience — the screen a person opens when they need to deal with arabic / rtl experience.</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3857,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Simple Registration &amp; OTP</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
@@ -3872,7 +3870,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
+          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3882,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Maintenance / Upgrade Page</t>
+          <t>Arabic / RTL Experience</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -3897,7 +3895,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
+          <t>Choose the app's language; Arabic turns the whole app right to left.</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3907,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
@@ -3922,7 +3920,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>The Plan tab: tell the venue who is coming, when, at what pace and what you like, and get a day-by-day plan.</t>
+          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3932,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Suggested Itineraries</t>
+          <t>Maintenance / Upgrade Page</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
@@ -3947,7 +3945,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Ready-made day plans for this venue that a guest can take instead of answering questions.</t>
+          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3957,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Your Plan</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -3972,7 +3970,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>The plan, day by day: swap, remove or add items, undo, add Fast Track, then book the whole plan.</t>
+          <t>The Plan tab: tell the venue who is coming, when, at what pace and what you like, and get a day-by-day plan.</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3982,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>AI Planner</t>
+          <t>Suggested Itineraries</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -3997,7 +3995,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Ask the planner in your own words to change the plan; it refines the rules plan, and the rules plan stays if AI is unavailable.</t>
+          <t>Ready-made day plans for this venue that a guest can take instead of answering questions.</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4007,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Dynamic QR Ticket</t>
+          <t>Your Plan</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
@@ -4022,7 +4020,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Find dynamic qr ticket for this venue.</t>
+          <t>The plan, day by day: swap, remove or add items, undo, add Fast Track, then book the whole plan.</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4032,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Plan in Progress</t>
+          <t>AI Planner</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4047,7 +4045,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Today's plan while you are in the venue, re-ordered against live waits.</t>
+          <t>Ask the planner in your own words to change the plan; it refines the rules plan, and the rules plan stays if AI is unavailable.</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4057,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Explore – Search Results</t>
+          <t>Dynamic QR Ticket</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
@@ -4072,7 +4070,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Find something when you do not know what it is called.</t>
+          <t>Show the live ticket code at the gate.</t>
         </is>
       </c>
     </row>
@@ -4084,20 +4082,20 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Wallet Overview</t>
+          <t>Plan in Progress</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>Today's plan while you are in the venue, re-ordered against live waits.</t>
         </is>
       </c>
     </row>
@@ -4109,20 +4107,20 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Ticket Transfer</t>
+          <t>Explore – Search Results</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Work with ticket transfer for this venue.</t>
+          <t>Find something when you do not know what it is called.</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4132,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Memberships</t>
+          <t>Wallet Overview</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4147,7 +4145,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Find memberships for this venue.</t>
+          <t>My wallet: balance, activity and auto top-up, and what is due or refundable at exit.</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4157,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Ticket Transfer</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4172,7 +4170,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Find my reservations for this venue.</t>
+          <t>Work with ticket transfer for this venue.</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4182,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Reservation Details</t>
+          <t>Memberships</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
@@ -4197,7 +4195,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>See reservation details for this venue.</t>
+          <t>Find memberships for this venue.</t>
         </is>
       </c>
     </row>
@@ -4209,12 +4207,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Order History</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
@@ -4222,7 +4220,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Find order history (wallet) for this venue.</t>
+          <t>Find my reservations for this venue.</t>
         </is>
       </c>
     </row>
@@ -4234,12 +4232,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Interactive Map</t>
+          <t>Reservation Details</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
@@ -4247,7 +4245,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>See where things are in relation to each other.</t>
+          <t>See reservation details for this venue.</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4257,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Attraction Wait Times</t>
+          <t>Order History</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
@@ -4272,7 +4270,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>See attraction wait times for this venue.</t>
+          <t>My orders at this venue, with their tax documents; transfer tickets or ask for a refund from here.</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4282,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>Interactive Map</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -4297,7 +4295,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Order food to where the guest is sitting, or for collection.</t>
+          <t>See where things are in relation to each other.</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4307,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>Attraction Wait Times</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -4322,7 +4320,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Track an order to the point it reaches the guest.</t>
+          <t>See attraction wait times for this venue.</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4332,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Retail / Merchandise</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
@@ -4347,7 +4345,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Find retail / merchandise for this venue.</t>
+          <t>Order food to where the guest is sitting, or for collection.</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4357,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Venue Info &amp; Services</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -4372,7 +4370,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>See venue info &amp; services for this venue.</t>
+          <t>Watch it being made, and see the table bill; it is paid at the table.</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4382,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>Retail / Merchandise</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
@@ -4397,7 +4395,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Work with in-venue notifications for this venue.</t>
+          <t>Buy merchandise and collect it on the way out, or have it delivered home.</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4407,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>Venue Info &amp; Services</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
@@ -4422,7 +4420,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>The screen this app sits on. Everything else is entered from here and returns to it.</t>
+          <t>How to reach the venue, its contact details, and where to eat.</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4432,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Chat</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -4447,7 +4445,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Add ai concierge – chat for this venue.</t>
+          <t>Work with in-venue notifications for this venue.</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4457,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Contextual Help</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -4472,7 +4470,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Ask, and be answered or handed to a person.</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4482,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>AI Concierge – Chat</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
@@ -4497,7 +4495,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>See lost &amp; found for this venue.</t>
+          <t>Talk to Sahli: the answers, and a person when Sahli cannot help.</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4507,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>AI Concierge – Contextual Help</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
@@ -4522,7 +4520,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Your points, your tier, and what is within reach.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4532,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
@@ -4547,7 +4545,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Find offers &amp; promotions for this venue.</t>
+          <t>See lost &amp; found for this venue.</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4557,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; Support</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
@@ -4572,7 +4570,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Your points, your tier, and what is within reach.</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4582,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Multi-Currency &amp; Pricing</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
@@ -4597,7 +4595,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>See prices in your own currency, in the app, before and during the visit.</t>
+          <t>Find offers &amp; promotions for this venue.</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4607,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Ticket Delivery &amp; Sharing</t>
+          <t>Help &amp; Support</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
@@ -4622,7 +4620,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Find ticket delivery &amp; sharing for this venue.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4632,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Upsell / Cross-Sell</t>
+          <t>Multi-Currency &amp; Pricing</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
@@ -4647,7 +4645,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>See upsell / cross-sell for this venue.</t>
+          <t>Choose the currency you see prices in and pay in.</t>
         </is>
       </c>
     </row>
@@ -4659,12 +4657,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Interactive Seat Selection</t>
+          <t>Ticket Delivery &amp; Sharing</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
@@ -4672,7 +4670,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>See interactive seat selection for this venue.</t>
+          <t>Find ticket delivery &amp; sharing for this venue.</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4682,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Bundle Package</t>
+          <t>Upsell / Cross-Sell</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -4697,7 +4695,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>See bundle package for this venue.</t>
+          <t>See upsell / cross-sell for this venue.</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4707,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Information</t>
+          <t>Interactive Seat Selection</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
@@ -4722,7 +4720,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Step-free routes, facilities and what to expect.</t>
+          <t>See interactive seat selection for this venue.</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4732,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>Bundle Package</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
@@ -4747,7 +4745,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Decide on a dish, choose modifiers, check allergens.</t>
+          <t>See bundle package for this venue.</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4757,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Privacy &amp; My Data</t>
+          <t>Accessibility Information</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
@@ -4772,7 +4770,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
+          <t>Step-free routes, facilities and what to expect.</t>
         </is>
       </c>
     </row>
@@ -4784,12 +4782,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Refunds &amp; Resale</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
@@ -4797,7 +4795,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
+          <t>Decide on a dish, choose modifiers, check allergens.</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4807,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; My Cases</t>
+          <t>Shop &amp; Drop Collection</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
@@ -4822,7 +4820,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
+          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4832,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Face Pass</t>
+          <t>Privacy &amp; My Data</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -4847,7 +4845,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>🔴 **Biometric enrolment had no guest-facing consent step.** `enrolFacePass` was callable by a guest and reachable from nowhere, which means enrolment was happening at a desk with somebody else operat</t>
+          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
         </is>
       </c>
     </row>
@@ -4859,12 +4857,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Reserve a Table</t>
+          <t>Refunds &amp; Resale</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
@@ -4872,7 +4870,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas, loungers and other spots on a venue map are booked on GST-074 (decided 29 September, rev 3 REV3-15 and GAP-C2, superseding audit R073 (c)). A deposit only where the venue enabled one (rev 3 REV3-8b, superseding audit R077 (a)).</t>
+          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4882,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Payment Methods</t>
+          <t>Help &amp; My Cases</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
@@ -4897,7 +4895,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
+          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
         </is>
       </c>
     </row>
@@ -4909,12 +4907,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Share &amp; Group Booking</t>
+          <t>Face Pass</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
@@ -4922,7 +4920,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
+          <t>Register or remove my face for gate entry on my pass, or a linked child's with my consent as guardian.</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4932,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Sign-in</t>
+          <t>Reserve a Table</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
@@ -4947,7 +4945,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. Two-step verification where a venue of the tenant enabled it (decided 29 September, rev 3 GAP-B1, per venue).</t>
+          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas, loungers and other spots on a venue map are booked on GST-074 (decided 29 September, rev 3 REV3-15 and GAP-C2, superseding audit R073 (c)). A deposit only where the venue enabled one (rev 3 REV3-8b, superseding audit R077 (a)).</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4957,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Add to Calendar / Reminders</t>
+          <t>Payment Methods</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -4968,11 +4966,11 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Find add to calendar / reminders for this venue.</t>
+          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
         </is>
       </c>
     </row>
@@ -4984,20 +4982,20 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Saved Items / Wishlist</t>
+          <t>Share &amp; Group Booking</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
         </is>
       </c>
     </row>
@@ -5009,20 +5007,20 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>Security &amp; Sign-in</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. Two-step verification where a venue of the tenant enabled it (decided 29 September, rev 3 GAP-B1, per venue).</t>
         </is>
       </c>
     </row>
@@ -5034,12 +5032,12 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>Add to Calendar / Reminders</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
@@ -5047,7 +5045,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>Find add to calendar / reminders for this venue.</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5057,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reservation Confirmed</t>
+          <t>Saved Items / Wishlist</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
@@ -5072,7 +5070,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5082,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Feedback &amp; Ratings</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
@@ -5097,7 +5095,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Work with feedback &amp; ratings for this venue.</t>
+          <t>Hold a place in a ride queue without standing in it.</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5107,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>At the Venue</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -5122,7 +5120,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Everything live at the venue in one place: map, waits, food, shows, shop and services, with what is happening now.</t>
+          <t>Choose a car park and add parking to the basket; change the plate on parking already bought.</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5132,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Resource Booking – Cabana</t>
+          <t>Parking – Reservation Confirmed</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
@@ -5147,7 +5145,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Book a cabana or other capacity-based resource.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5157,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Resource Availability (Cabana)</t>
+          <t>Feedback &amp; Ratings</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
@@ -5172,7 +5170,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>See which cabanas are free, by area and date, before choosing one.</t>
+          <t>Tell the venue how the visit went, answer a survey it sent, or report a problem.</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5182,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Shop &amp; Drop Collection</t>
+          <t>At the Venue</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
@@ -5197,7 +5195,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
+          <t>Everything live at the venue in one place: map, waits, food, shows, shop and services, with what is happening now.</t>
         </is>
       </c>
     </row>
@@ -5209,12 +5207,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Newsletter &amp; Preferences</t>
+          <t>Resource Booking – Cabana</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
@@ -5222,7 +5220,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>What we may send you, and how.</t>
+          <t>Book a cabana or other capacity-based resource.</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5232,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Map Booking — Cabanas &amp; Spots</t>
+          <t>Resource Availability (Cabana)</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -5247,7 +5245,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
+          <t>See which cabanas are free, by area and date, before choosing one.</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5257,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Book a Space by the Hour</t>
+          <t>Newsletter &amp; Preferences</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
@@ -5272,7 +5270,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
+          <t>What we may send you, and how.</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5282,12 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Route &amp; Schedule</t>
+          <t>Map Booking — Cabanas &amp; Spots</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
@@ -5297,7 +5295,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Find a departure between two stations for a date and a time of day.</t>
+          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5307,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Route &amp; Passengers</t>
+          <t>Book a Space by the Hour</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
@@ -5322,7 +5320,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>See the chosen departure's stops and map, add the passengers and buy the trip.</t>
+          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5332,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Multi-trip Passes</t>
+          <t>Intercity Trip — Route &amp; Schedule</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -5347,7 +5345,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Buy a 5- or 10-trip card or a weekly or monthly unlimited pass for a station pair.</t>
+          <t>Find a departure between two stations for a date and a time of day.</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5357,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Intercity Trip — Favourite Routes</t>
+          <t>Intercity Trip — Route &amp; Passengers</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -5372,57 +5370,57 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Rebook a saved route in two taps, or remove it.</t>
+          <t>See the chosen departure's stops and map, add the passengers and buy the trip.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Site Builder</t>
+          <t>Intercity Trip — Multi-trip Passes</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Build a working site in about 30 minutes: pick a preset, then walk seven saved steps (venue and modules, ticketing flows, compose steps, Help me choose, look and feel, mobile app, preview and publish), each opening the full screen for its details. **The preset keeps the minimum path short (M24-05)**: it proposes the modules, the booking flows with their default step order, the home sections and the mobile tabs, so the only things an operator must supply are a logo, four colours and a Publish; everything else keeps the preset or the contract default and can be refined later.</t>
+          <t>Buy a 5- or 10-trip card or a weekly or monthly unlimited pass for a station pair.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>White Labelling</t>
+          <t>Guest App - Mobile</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Booking Flows</t>
+          <t>Intercity Trip — Favourite Routes</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Pick the venue's booking flows, turn optional steps on or off, set the step order within the allowed limits with a live preview, assign flows to products and categories, and validate them before they publish with the site.</t>
+          <t>Rebook a saved route in two taps, or remove it.</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5432,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>App Build &amp; Store Publishing</t>
+          <t>Site Builder</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -5447,7 +5445,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Get the tenant's own app into the App Store and Google Play under the client's own accounts — checklist, store listing, request a build, download or submit it, follow its review — with a guide for the steps only the client can take.</t>
+          <t>Build a working site in about 30 minutes: pick a preset, then walk seven saved steps (venue and modules, ticketing flows, compose steps, Help me choose, look and feel, mobile app, preview and publish), each opening the full screen for its details. **The preset keeps the minimum path short (M24-05)**: it proposes the modules, the booking flows with their default step order, the home sections and the mobile tabs, so the only things an operator must supply are a logo, four colours and a Publish; everything else keeps the preset or the contract default and can be refined later.</t>
         </is>
       </c>
     </row>
@@ -5459,20 +5457,20 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>White-Label Branding Management</t>
+          <t>Booking Flows</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>See white-label branding management for this venue.</t>
+          <t>Pick the venue's booking flows, turn optional steps on or off, set the step order within the allowed limits with a live preview, assign flows to products and categories, and validate them before they publish with the site.</t>
         </is>
       </c>
     </row>
@@ -5484,20 +5482,20 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate Management</t>
+          <t>App Build &amp; Store Publishing</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>See domain &amp; certificate management for this venue.</t>
+          <t>Get the tenant's own app into the App Store and Google Play under the client's own accounts — checklist, store listing, request a build, download or submit it, follow its review — with a guide for the steps only the client can take.</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5507,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Localisation &amp; Language Pack</t>
+          <t>White-Label Branding Management</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -5522,7 +5520,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Configure localisation &amp; language pack for this venue.</t>
+          <t>Support a tenant's branding from the platform console, inside an open grant.</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5532,12 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Tenant Workspace</t>
+          <t>Domain &amp; Certificate Management</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
@@ -5547,7 +5545,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Land a tenant somewhere that shows what is live and what is not, and hold step 1 of the Site Builder (venue and modules).</t>
+          <t>Support a tenant's custom domains and certificates from the platform console.</t>
         </is>
       </c>
     </row>
@@ -5559,12 +5557,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Brand Kit</t>
+          <t>Interface Languages</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
@@ -5572,7 +5570,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Set the things every surface reads.</t>
+          <t>Add or select a tenant's interface languages beyond English and Arabic, inside an open grant, and see how far the interface strings reach in each.</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5582,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Tenant Workspace</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -5597,7 +5595,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Choose the two typefaces and the scale under them.</t>
+          <t>Land a tenant somewhere that shows what is live and what is not, and hold step 1 of the Site Builder (venue and modules).</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5607,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Logo &amp; Assets</t>
+          <t>Brand Kit</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -5622,7 +5620,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Hold the marks every surface needs, at the sizes it needs them, and the mobile app's intro video (Site Builder steps 5 and 6).</t>
+          <t>Set the things every surface reads.</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5632,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Theme Editor</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -5647,7 +5645,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Tune the theme and watch it apply everywhere at once.</t>
+          <t>Choose the two typefaces, Latin and Arabic; the type scale is TICVAI's fixed token set.</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5657,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Component Preview</t>
+          <t>Logo &amp; Assets</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -5672,7 +5670,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Check the theme against the components that carry it.</t>
+          <t>Hold the marks every surface needs, at the sizes it needs them, and the mobile app's intro video (Site Builder steps 5 and 6).</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5682,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Page Builder</t>
+          <t>Theme Editor</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -5697,7 +5695,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
+          <t>Tune the theme and watch it apply everywhere at once.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5707,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Content Blocks</t>
+          <t>Component Preview</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -5722,7 +5720,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Define what a block can and cannot contain, and set the banners (Site Builder step 5).</t>
+          <t>Check the theme against the components that carry it.</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5732,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Navigation &amp; Menus</t>
+          <t>Page Builder</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -5747,7 +5745,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Decide what appears in the header, the footer and the mobile tab bar, with the Buy tickets button (Site Builder steps 5 and 6).</t>
+          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5757,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Media Library</t>
+          <t>Content Blocks</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -5772,7 +5770,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Hold the imagery, and know where it is used.</t>
+          <t>Define what a block can and cannot contain, and set the banners (Site Builder step 5).</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5782,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Translations</t>
+          <t>Navigation &amp; Menus</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -5797,7 +5795,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Fill in what every language is missing.</t>
+          <t>Three editors, each saved on its own: the header, the footer and the mobile tab bar with the Buy tickets button (Site Builder steps 5 and 6); and the links a tenant's own site uses to deep-link in.</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5807,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>RTL Preview</t>
+          <t>Media Library</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -5822,7 +5820,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>See the site as an Arabic reader sees it.</t>
+          <t>Hold the imagery, and know where it is used.</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5832,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SEO &amp; Metadata</t>
+          <t>Translations</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -5847,7 +5845,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Control how a page looks everywhere it is not the page.</t>
+          <t>Fill in what every language is missing.</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5857,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Publishing Workflow</t>
+          <t>RTL Preview</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -5872,7 +5870,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Move a change from draft to live, with someone accountable (Site Builder step 7).</t>
+          <t>See the site as an Arabic reader sees it.</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5882,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Version History</t>
+          <t>SEO &amp; Metadata</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -5897,7 +5895,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
+          <t>Control how a page looks everywhere it is not the page.</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5907,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Site Settings</t>
+          <t>Publishing Workflow</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -5922,7 +5920,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>The values the whole site inherits from, and the venue-wide booking settings each venue may override (decided 29 September, rev 3 CFG-11); the settings of one flow are on CMS-103 (W12).</t>
+          <t>Move a change from draft to live, with someone accountable (Site Builder step 7).</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5932,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate</t>
+          <t>Version History</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -5947,7 +5945,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Point the tenant’s own domain at their site.</t>
+          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5957,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Consent &amp; Legal</t>
+          <t>Site Settings</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -5972,7 +5970,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Manage the notices every consent is captured against, and the booking consent questions a venue asks ("Are you able to swim?", "I accept the risk"), with the record of every answer (decided 29 September, rev 3 REV3-26).</t>
+          <t>The values the whole site inherits from, and the venue-wide booking settings each venue may override (decided 29 September, rev 3 CFG-11); the settings of one flow are on CMS-103 (W12).</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5982,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>User Access</t>
+          <t>Domain &amp; Certificate</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -5997,7 +5995,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Say who in the tenant may change what.</t>
+          <t>Point the tenant’s own domain at their site.</t>
         </is>
       </c>
     </row>
@@ -6009,25 +6007,100 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
+          <t>Consent &amp; Legal</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Manage the notices every consent is captured against, and the booking consent questions a venue asks ("Are you able to swim?", "I accept the risk"), with the record of every answer (decided 29 September, rev 3 REV3-26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>User Access</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Say who in the tenant may change what.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
           <t>Help Me Choose</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>White Label</t>
         </is>
       </c>
-      <c r="D194" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="D196" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Set up a venue's Help me choose so its answers filter the catalogue, review the question set the assistant proposes from the venue's products, preview the filtered list and publish it (Site Builder step 4).</t>
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>White Labelling</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Module Activation &amp; Dependency Validation</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Tenants &amp; Licensing</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Activate the modules purchased in Board 4/5 and verify all required dependencies.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E194"/>
+  <autoFilter ref="A1:E197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -485,11 +485,9 @@
         <v>42</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>13</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -507,14 +505,10 @@
         <v>50</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>7</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Account &amp; Self-Service, Booking &amp; Selection, Cart &amp; Checkout, Discovery &amp; Browse, Engagement &amp; Support, High-Demand Access, In-venue Services, Membership, Loyalty &amp; Value, Promotions, Retail, Support, System States, Ticketing, Transport</t>
@@ -531,14 +525,10 @@
         <v>77</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>16</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Account &amp; Self-Service, Booking &amp; Selection, Cart &amp; Checkout, Discovery, Discovery &amp; Browse, Engagement &amp; Support, High-Demand Access, In-Venue Experience, In-venue Services, Marketing, Membership, Loyalty &amp; Value, Promotions, Retail, Support, System States, Ticketing, Transport</t>
@@ -555,14 +545,10 @@
         <v>27</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Branding &amp; Localisation, Tenants &amp; Licensing, White Label</t>
@@ -1207,12 +1193,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sign In</t>
+          <t>Kitchen Operations Command Center</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -1220,7 +1206,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Authenticate the operator at the terminal and resolve the session every other screen on this app reads.</t>
+          <t>Kitchen Operations Command Center — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1218,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Begin Shift</t>
+          <t>Kitchen Display System (KDS)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -1245,7 +1231,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Count the opening float and open the till.</t>
+          <t>Kitchen Display System (KDS) — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1243,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sell — Ticket Catalogue</t>
+          <t>Order Firing &amp; Course Management</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -1270,7 +1256,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Find a product and add it to the cart.</t>
+          <t>Order Firing &amp; Course Management — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1268,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Sell — Timed Entry</t>
+          <t>Active Order Management &amp; Fulfilment Journey</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -1295,7 +1281,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Pick a date, a session and ticket quantities.</t>
+          <t>Follow one order from the till to the pass and out to the guest.</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1293,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Kitchen Station Workload &amp; Dynamic Routing</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -1320,7 +1306,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Take payment and complete the sale.</t>
+          <t>Kitchen Station Workload &amp; Dynamic Routing — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1318,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Held Orders</t>
+          <t>Expeditor &amp; Order Assembly</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -1345,7 +1331,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Find and resume a parked sale.</t>
+          <t>Expeditor &amp; Order Assembly — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1343,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Close Shift</t>
+          <t>Guest Collection, Buzzer &amp; Digital Notification</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -1370,7 +1356,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Count the drawer and close the till.</t>
+          <t>Guest Collection, Buzzer &amp; Digital Notification — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1368,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Add to Existing Ticket</t>
+          <t>Exceptions, Re-Fire &amp; Unavailable Items</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -1395,7 +1381,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Sell something onto media the guest is already carrying.</t>
+          <t>Exceptions, Re-Fire &amp; Unavailable Items — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1393,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Returns, Refunds &amp; Exchanges</t>
+          <t>SLA, Priority &amp; Service Rules</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -1420,7 +1406,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Take back a sale, refund it or exchange it, against the original receipt.</t>
+          <t>SLA, Priority &amp; Service Rules — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1418,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Omnichannel Order &amp; Fulfilment Center</t>
+          <t>Kitchen Performance, AI &amp; Operational Optimization</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -1445,7 +1431,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Omnichannel Order &amp; Fulfilment Center — from the client design board, 20 August.</t>
+          <t>Kitchen Performance, AI &amp; Operational Optimization — board 3 of the client F&amp;B design set.</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1443,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mobile POS, Event Sales &amp; Offline Operations</t>
+          <t>Sign In</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1470,7 +1456,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Keep selling while the till is offline, and see what the server refused when it syncs.</t>
+          <t>Authenticate the operator at the terminal and resolve the session every other screen on this app reads.</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1468,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Sales Exceptions, Controls &amp; Operational Actions</t>
+          <t>Begin Shift</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Sales Exceptions, Controls &amp; Operational Actions — from the client design board, 20 August.</t>
+          <t>Count the opening float and open the till.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1493,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cash Operations Dashboard</t>
+          <t>Sell — Ticket Catalogue</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1520,7 +1506,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>See the live cash position of every till, for a supervisor.</t>
+          <t>Find a product and add it to the cart.</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1518,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Till Configuration</t>
+          <t>Sell — Timed Entry</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1545,7 +1531,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Configure this till in place: its workstation settings, its peripherals and the cashier's deposit box.</t>
+          <t>Pick a date, a session and ticket quantities.</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1543,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cash In / Cash Out Operations</t>
+          <t>Sell — Seat Map</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1570,7 +1556,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Cash In / Cash Out Operations — from the client design board, 20 August.</t>
+          <t>Choose specific seats for a seated event.</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1568,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Safe Drop &amp; Cash Transfer Management</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1595,7 +1581,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Drop cash from a drawer to the safe when it passes the ceiling.</t>
+          <t>Take payment and complete the sale.</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1593,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Shift Templates &amp; Policies</t>
+          <t>Held Orders</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1620,7 +1606,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>See this till's shifts and the opening and closing rules they run under.</t>
+          <t>Find and resume a parked sale.</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1618,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Shift Exceptions &amp; Alerts</t>
+          <t>Close Shift</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1645,7 +1631,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Shift Exceptions &amp; Alerts — from the client design board, 20 August.</t>
+          <t>Count the drawer and close the till.</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1643,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sell — Food &amp; Drink</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1670,7 +1656,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>A guest orders food at a counter and pays.</t>
+          <t>See how the day is going from the terminal.</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1668,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Send to Kitchen</t>
+          <t>Staff Roster</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1695,7 +1681,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>The order goes to the pass and the guest is given a number.</t>
+          <t>See who is on duty and on which terminal.</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1693,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sell — Merchandise</t>
+          <t>Add to Existing Ticket</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1720,7 +1706,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>A guest buys merchandise at a counter.</t>
+          <t>Sell something onto media the guest is already carrying.</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1718,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Outlet Setup</t>
+          <t>Returns, Refunds &amp; Exchanges</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1745,7 +1731,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>A manager configures this outlet from the floor.</t>
+          <t>Take back a sale, refund it or exchange it, against the original receipt.</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1743,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Till Home</t>
+          <t>Omnichannel Order &amp; Fulfilment Center</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1770,7 +1756,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>The surface a cashier lands on after opening a shift, and the one they return to between sales.</t>
+          <t>Omnichannel Order &amp; Fulfilment Center — from the client design board, 20 August.</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1768,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Receipt &amp; Reprint</t>
+          <t>Mobile POS, Event Sales &amp; Offline Operations</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1795,7 +1781,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Reprint a receipt or reissue an entitlement when the guest is still at the counter.</t>
+          <t>Keep selling while the till is offline, and see what the server refused when it syncs.</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1793,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Guest Lookup</t>
+          <t>Sales Exceptions, Controls &amp; Operational Actions</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1820,7 +1806,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Find the guest in front of you, so the sale carries their entitlements and their wallet.</t>
+          <t>Sales Exceptions, Controls &amp; Operational Actions — from the client design board, 20 August.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1818,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Table Service</t>
+          <t>Cash Operations Dashboard</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1845,7 +1831,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Seat parties and close table visits from the floor.</t>
+          <t>See the live cash position of every till, for a supervisor.</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1843,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Order Queue</t>
+          <t>Till Configuration</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1870,7 +1856,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Watch orders move from received to handed over, and act on the ones that stall.</t>
+          <t>Configure this till in place: its workstation settings, its peripherals and the cashier's deposit box.</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1868,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Sales Journal</t>
+          <t>Cash In / Cash Out Operations</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1895,7 +1881,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Find a sale this till made and act on it — reprint or email the receipt, issue a tax invoice, reload it into the cart, or hand it to returns.</t>
+          <t>Cash In / Cash Out Operations — from the client design board, 20 August.</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1893,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Reservations &amp; Group Arrivals</t>
+          <t>Safe Drop &amp; Cash Transfer Management</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1920,7 +1906,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Hold a sale without payment, and take payment when the guest or the group arrives.</t>
+          <t>Drop cash from a drawer to the safe when it passes the ceiling.</t>
         </is>
       </c>
     </row>
@@ -1932,20 +1918,20 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Operations Command Center</t>
+          <t>Shift Templates &amp; Policies</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Operations Command Center — board 3 of the client F&amp;B design set.</t>
+          <t>See this till's shifts and the opening and closing rules they run under.</t>
         </is>
       </c>
     </row>
@@ -1957,20 +1943,20 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Display System (KDS)</t>
+          <t>Shift Exceptions &amp; Alerts</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Display System (KDS) — board 3 of the client F&amp;B design set.</t>
+          <t>Shift Exceptions &amp; Alerts — from the client design board, 20 August.</t>
         </is>
       </c>
     </row>
@@ -1982,20 +1968,20 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Order Firing &amp; Course Management</t>
+          <t>Sell — Food &amp; Drink</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Order Firing &amp; Course Management — board 3 of the client F&amp;B design set.</t>
+          <t>A guest orders food at a counter and pays.</t>
         </is>
       </c>
     </row>
@@ -2007,20 +1993,20 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Active Order Management &amp; Fulfilment Journey</t>
+          <t>Send to Kitchen</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Follow one order from the till to the pass and out to the guest.</t>
+          <t>The order goes to the pass and the guest is given a number.</t>
         </is>
       </c>
     </row>
@@ -2032,20 +2018,20 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Station Workload &amp; Dynamic Routing</t>
+          <t>Sell — Merchandise</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Station Workload &amp; Dynamic Routing — board 3 of the client F&amp;B design set.</t>
+          <t>A guest buys merchandise at a counter.</t>
         </is>
       </c>
     </row>
@@ -2057,20 +2043,20 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Expeditor &amp; Order Assembly</t>
+          <t>Outlet Setup</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Expeditor &amp; Order Assembly — board 3 of the client F&amp;B design set.</t>
+          <t>A manager configures this outlet from the floor.</t>
         </is>
       </c>
     </row>
@@ -2082,20 +2068,20 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Guest Collection, Buzzer &amp; Digital Notification</t>
+          <t>Till Home</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Guest Collection, Buzzer &amp; Digital Notification — board 3 of the client F&amp;B design set.</t>
+          <t>The surface a cashier lands on after opening a shift, and the one they return to between sales.</t>
         </is>
       </c>
     </row>
@@ -2107,20 +2093,20 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Exceptions, Re-Fire &amp; Unavailable Items</t>
+          <t>Receipt &amp; Reprint</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Exceptions, Re-Fire &amp; Unavailable Items — board 3 of the client F&amp;B design set.</t>
+          <t>Reprint a receipt or reissue an entitlement when the guest is still at the counter.</t>
         </is>
       </c>
     </row>
@@ -2132,20 +2118,20 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SLA, Priority &amp; Service Rules</t>
+          <t>Guest Lookup</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>SLA, Priority &amp; Service Rules — board 3 of the client F&amp;B design set.</t>
+          <t>Find the guest in front of you, so the sale carries their entitlements and their wallet.</t>
         </is>
       </c>
     </row>
@@ -2157,20 +2143,20 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Performance, AI &amp; Operational Optimization</t>
+          <t>Table Service</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Performance, AI &amp; Operational Optimization — board 3 of the client F&amp;B design set.</t>
+          <t>Seat parties and close table visits from the floor.</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2168,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Sell — Seat Map</t>
+          <t>Order Queue</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2191,11 +2177,11 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Choose specific seats for a seated event.</t>
+          <t>Watch orders move from received to handed over, and act on the ones that stall.</t>
         </is>
       </c>
     </row>
@@ -2207,20 +2193,20 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Sales Journal</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>See how the day is going from the terminal.</t>
+          <t>Find a sale this till made and act on it — reprint or email the receipt, issue a tax invoice, reload it into the cart, or hand it to returns.</t>
         </is>
       </c>
     </row>
@@ -2232,20 +2218,20 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Staff Roster</t>
+          <t>Reservations &amp; Group Arrivals</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>See who is on duty and on which terminal.</t>
+          <t>Hold a sale without payment, and take payment when the guest or the group arrives.</t>
         </is>
       </c>
     </row>
@@ -2407,12 +2393,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Shopping Cart</t>
+          <t>Interactive Seat Selection</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -2420,7 +2406,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Review and confirm what is being bought.</t>
+          <t>Choose specific seats.</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2418,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Guest Details &amp; Attendee Forms</t>
+          <t>Add-ons &amp; Upsell</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2445,7 +2431,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Collect who is coming and how to reach them.</t>
+          <t>See add-ons &amp; upsell for this venue.</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2443,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Checkout — Payment</t>
+          <t>Wishlist</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2470,7 +2456,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Take payment and create the order.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2468,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Booking Confirmation</t>
+          <t>Shopping Cart</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2495,7 +2481,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Confirm the purchase and deliver the tickets.</t>
+          <t>Review and confirm what is being bought.</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2493,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Pay for a Booking</t>
+          <t>Guest Details &amp; Attendee Forms</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2520,7 +2506,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Pay for a booking somebody else took, without an account.</t>
+          <t>Collect who is coming and how to reach them.</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2518,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Login / Register</t>
+          <t>Checkout — Payment</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -2545,7 +2531,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the site, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
+          <t>Take payment and create the order.</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2543,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>My Account Dashboard</t>
+          <t>Booking Confirmation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -2570,7 +2556,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Everything I have with this venue at a glance: bookings, wallet, loyalty, challenges and invitations, each opening its own pane.</t>
+          <t>Confirm the purchase and deliver the tickets.</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2568,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>My Tickets</t>
+          <t>Pay for a Booking</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -2595,7 +2581,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>Pay for a booking somebody else took, without an account.</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2593,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Order History</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -2620,7 +2606,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Find order history for this venue.</t>
+          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2618,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Profile &amp; Preferences</t>
+          <t>Login / Register</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2645,7 +2631,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Correct your details, choose what we may send you, and record your needs.</t>
+          <t>Get a guest into the site, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2643,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Help Centre / FAQ</t>
+          <t>My Account Dashboard</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -2670,7 +2656,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Everything I have with this venue at a glance: bookings, wallet, loyalty, challenges and invitations, each opening its own pane.</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2668,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Contact &amp; Venue Information</t>
+          <t>My Tickets</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -2695,7 +2681,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Find contact &amp; venue information for this venue.</t>
+          <t>Find my tickets for this venue.</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2693,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Error / Sold Out / Maintenance</t>
+          <t>Order History</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -2720,7 +2706,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
+          <t>Find order history for this venue.</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2718,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Ticket Transfer</t>
+          <t>Profile &amp; Preferences</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -2745,7 +2731,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Send a ticket to someone else, and see what you have sent.</t>
+          <t>Correct your details, choose what we may send you, and record your needs.</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2743,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Multi-Currency &amp; Pricing</t>
+          <t>Wallet &amp; Gift Cards</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -2770,7 +2756,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Choose the currency you see prices in and pay in.</t>
+          <t>See wallet &amp; gift cards for this venue.</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2768,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Plan Your Visit</t>
+          <t>Membership Plans</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -2795,7 +2781,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Plan a visit on the website: answer six questions, get a day-by-day plan, edit it, and book it in one go.</t>
+          <t>Membership Plans — the screen a person opens when they need to deal with membership plans.</t>
         </is>
       </c>
     </row>
@@ -2807,20 +2793,20 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Interactive Seat Selection</t>
+          <t>Membership Management</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Choose specific seats.</t>
+          <t>Work with membership management for this venue.</t>
         </is>
       </c>
     </row>
@@ -2832,20 +2818,20 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Add-ons &amp; Upsell</t>
+          <t>Devices, Wishlist &amp; Consent</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>See add-ons &amp; upsell for this venue.</t>
+          <t>Your devices, security, cookie choices and data rights.</t>
         </is>
       </c>
     </row>
@@ -2857,20 +2843,20 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Help Centre / FAQ</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -2882,20 +2868,20 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Wallet &amp; Gift Cards</t>
+          <t>Survey &amp; Feedback</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>See wallet &amp; gift cards for this venue.</t>
+          <t>Tell the venue how the visit went, answer a survey it sent, or report a problem.</t>
         </is>
       </c>
     </row>
@@ -2907,20 +2893,20 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Membership Plans</t>
+          <t>Newsletter Subscription</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Membership Plans — the screen a person opens when they need to deal with membership plans.</t>
+          <t>Choose which newsletters you receive and on which channel, or leave one from its email link.</t>
         </is>
       </c>
     </row>
@@ -2932,20 +2918,20 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Membership Management</t>
+          <t>Contact &amp; Venue Information</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Work with membership management for this venue.</t>
+          <t>Find contact &amp; venue information for this venue.</t>
         </is>
       </c>
     </row>
@@ -2957,20 +2943,20 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Newsletter Subscription</t>
+          <t>Error / Sold Out / Maintenance</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Choose which newsletters you receive and on which channel, or leave one from its email link.</t>
+          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2968,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Ticket Transfer</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2991,11 +2977,11 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>What you have booked and not yet paid for.</t>
+          <t>Send a ticket to someone else, and see what you have sent.</t>
         </is>
       </c>
     </row>
@@ -3007,20 +2993,20 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>What is on, and what applies to you.</t>
+          <t>What you have booked and not yet paid for.</t>
         </is>
       </c>
     </row>
@@ -3032,20 +3018,20 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Merchandise, browsable before you arrive.</t>
+          <t>What is on, and what applies to you.</t>
         </is>
       </c>
     </row>
@@ -3057,20 +3043,20 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Order food from a table, a lounger or a seat.</t>
+          <t>Merchandise, browsable before you arrive.</t>
         </is>
       </c>
     </row>
@@ -3082,20 +3068,20 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>What is in it, and what may be changed.</t>
+          <t>Report something you left behind.</t>
         </is>
       </c>
     </row>
@@ -3107,20 +3093,20 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>Multi-Currency &amp; Pricing</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Watch it being made, and see the table bill; it is paid at the table.</t>
+          <t>Choose the currency you see prices in and pay in.</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3118,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Venue Map &amp; Wait Times</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3141,11 +3127,11 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Where things are, and how long they take.</t>
+          <t>Order food from a table, a lounger or a seat.</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3143,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3166,11 +3152,11 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hold a place without standing in one.</t>
+          <t>What is in it, and what may be changed.</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3168,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3191,11 +3177,11 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Reserve a facility before arriving.</t>
+          <t>Watch it being made, and see the table bill; it is paid at the table.</t>
         </is>
       </c>
     </row>
@@ -3207,20 +3193,20 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Retail &amp; Shop and Drop</t>
+          <t>Venue Map &amp; Wait Times</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Buy merchandise and collect it on the way out.</t>
+          <t>Where things are, and how long they take.</t>
         </is>
       </c>
     </row>
@@ -3232,20 +3218,20 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Points, tier, and what the next one needs.</t>
+          <t>Hold a place without standing in one.</t>
         </is>
       </c>
     </row>
@@ -3257,20 +3243,20 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Ask, and be answered or handed to a person.</t>
+          <t>Reserve a facility before arriving.</t>
         </is>
       </c>
     </row>
@@ -3282,20 +3268,20 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Help Centre &amp; Accessibility</t>
+          <t>Retail &amp; Shop and Drop</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Answers, policies and the accessibility statement.</t>
+          <t>Buy merchandise and collect it on the way out.</t>
         </is>
       </c>
     </row>
@@ -3307,20 +3293,20 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Queue calls, order updates, venue notices.</t>
+          <t>Points, tier, and what the next one needs.</t>
         </is>
       </c>
     </row>
@@ -3332,20 +3318,20 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Wishlist</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>Ask, and be answered or handed to a person.</t>
         </is>
       </c>
     </row>
@@ -3357,20 +3343,20 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Devices, Wishlist &amp; Consent</t>
+          <t>Help Centre &amp; Accessibility</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Your devices, security, cookie choices and data rights.</t>
+          <t>Answers, policies and the accessibility statement.</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3368,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Survey &amp; Feedback</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3391,11 +3377,11 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Tell the venue how the visit went, answer a survey it sent, or report a problem.</t>
+          <t>Queue calls, order updates, venue notices.</t>
         </is>
       </c>
     </row>
@@ -3407,20 +3393,20 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Map Booking — Cabanas &amp; Spots</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Report something you left behind.</t>
+          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3418,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Map Booking — Cabanas &amp; Spots</t>
+          <t>Book a Space by the Hour</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3441,11 +3427,11 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Pick a specific cabana, lounger or other spot on the venue map and hold it while you book.</t>
+          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
         </is>
       </c>
     </row>
@@ -3457,20 +3443,20 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Book a Space by the Hour</t>
+          <t>Transport — Route &amp; Schedule</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Book a meeting room or other space for a start time and a length; the price is the room rate for that length.</t>
+          <t>Find a departure between two stations and buy a trip, a multi-trip or unlimited pass, or rebook a saved route.</t>
         </is>
       </c>
     </row>
@@ -3482,20 +3468,20 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Transport — Route &amp; Schedule</t>
+          <t>Plan Your Visit</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Find a departure between two stations and buy a trip, a multi-trip or unlimited pass, or rebook a saved route.</t>
+          <t>Plan a visit on the website: answer six questions, get a day-by-day plan, edit it, and book it in one go.</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3743,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>My Tickets</t>
+          <t>Wallet Overview</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
@@ -3770,7 +3756,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>My wallet: balance, activity and auto top-up, and what is due or refundable at exit.</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3768,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Ticket Details</t>
+          <t>My Tickets</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -3795,7 +3781,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Find ticket details for this venue.</t>
+          <t>Find my tickets for this venue.</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3793,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Ticket Details</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -3820,7 +3806,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>What we hold about a guest, and what they can change.</t>
+          <t>Find ticket details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3832,12 +3818,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Checkout Entry</t>
+          <t>Ticket Transfer</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Cart &amp; Checkout</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
@@ -3845,7 +3831,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Take the money, and be unambiguous about whether it worked.</t>
+          <t>Work with ticket transfer for this venue.</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3843,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Simple Registration &amp; OTP</t>
+          <t>Memberships</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
@@ -3870,7 +3856,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
+          <t>Find memberships for this venue.</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3868,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience</t>
+          <t>My Reservations</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
@@ -3895,7 +3881,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Choose the app's language; Arabic turns the whole app right to left.</t>
+          <t>Find my reservations for this venue.</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3893,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Branded Queue / Waiting Room</t>
+          <t>Reservation Details</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>High-Demand Access</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
@@ -3920,7 +3906,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
+          <t>See reservation details for this venue.</t>
         </is>
       </c>
     </row>
@@ -3932,12 +3918,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Maintenance / Upgrade Page</t>
+          <t>Add to Calendar / Reminders</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>System States</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
@@ -3945,7 +3931,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
+          <t>Find add to calendar / reminders for this venue.</t>
         </is>
       </c>
     </row>
@@ -3957,12 +3943,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Order History</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
@@ -3970,7 +3956,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>The Plan tab: tell the venue who is coming, when, at what pace and what you like, and get a day-by-day plan.</t>
+          <t>My orders at this venue, with their tax documents; transfer tickets or ask for a refund from here.</t>
         </is>
       </c>
     </row>
@@ -3982,12 +3968,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Suggested Itineraries</t>
+          <t>Saved Items / Wishlist</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
@@ -3995,7 +3981,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Ready-made day plans for this venue that a guest can take instead of answering questions.</t>
+          <t>Find the right one quickly, and act on it without opening it.</t>
         </is>
       </c>
     </row>
@@ -4007,12 +3993,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Your Plan</t>
+          <t>Interactive Map</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
@@ -4020,7 +4006,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>The plan, day by day: swap, remove or add items, undo, add Fast Track, then book the whole plan.</t>
+          <t>See where things are in relation to each other.</t>
         </is>
       </c>
     </row>
@@ -4032,12 +4018,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>AI Planner</t>
+          <t>Attraction Wait Times</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
@@ -4045,7 +4031,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Ask the planner in your own words to change the plan; it refines the rules plan, and the rules plan stays if AI is unavailable.</t>
+          <t>See attraction wait times for this venue.</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4043,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Dynamic QR Ticket</t>
+          <t>Virtual Queue</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
@@ -4070,7 +4056,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Show the live ticket code at the gate.</t>
+          <t>Hold a place in a ride queue without standing in it.</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4068,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Plan in Progress</t>
+          <t>F&amp;B – Browse &amp; Order</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
@@ -4095,7 +4081,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Today's plan while you are in the venue, re-ordered against live waits.</t>
+          <t>Order food to where the guest is sitting, or for collection.</t>
         </is>
       </c>
     </row>
@@ -4107,12 +4093,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Explore – Search Results</t>
+          <t>F&amp;B – Order Tracking</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Discovery</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
@@ -4120,7 +4106,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Find something when you do not know what it is called.</t>
+          <t>Watch it being made, and see the table bill; it is paid at the table.</t>
         </is>
       </c>
     </row>
@@ -4132,20 +4118,20 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Wallet Overview</t>
+          <t>Retail / Merchandise</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>My wallet: balance, activity and auto top-up, and what is due or refundable at exit.</t>
+          <t>Buy merchandise and collect it on the way out, or have it delivered home.</t>
         </is>
       </c>
     </row>
@@ -4157,20 +4143,20 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Ticket Transfer</t>
+          <t>Parking – Reserve &amp; Pay</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Work with ticket transfer for this venue.</t>
+          <t>Choose a car park and add parking to the basket; change the plate on parking already bought.</t>
         </is>
       </c>
     </row>
@@ -4182,20 +4168,20 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Memberships</t>
+          <t>Parking – Reservation Confirmed</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Find memberships for this venue.</t>
+          <t>Confirm it worked, and give them what they need to prove it.</t>
         </is>
       </c>
     </row>
@@ -4207,20 +4193,20 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>My Reservations</t>
+          <t>Venue Info &amp; Services</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Find my reservations for this venue.</t>
+          <t>How to reach the venue, its contact details, and where to eat.</t>
         </is>
       </c>
     </row>
@@ -4232,20 +4218,20 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Reservation Details</t>
+          <t>In-Venue Notifications</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>See reservation details for this venue.</t>
+          <t>Work with in-venue notifications for this venue.</t>
         </is>
       </c>
     </row>
@@ -4257,20 +4243,20 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Order History</t>
+          <t>AI Concierge – Home</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>My orders at this venue, with their tax documents; transfer tickets or ask for a refund from here.</t>
+          <t>Ask, and be answered or handed to a person.</t>
         </is>
       </c>
     </row>
@@ -4282,20 +4268,20 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Interactive Map</t>
+          <t>AI Concierge – Chat</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>See where things are in relation to each other.</t>
+          <t>Talk to Sahli: the answers, and a person when Sahli cannot help.</t>
         </is>
       </c>
     </row>
@@ -4307,20 +4293,20 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Attraction Wait Times</t>
+          <t>AI Concierge – Contextual Help</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>See attraction wait times for this venue.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4332,20 +4318,20 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Browse &amp; Order</t>
+          <t>Lost &amp; Found</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Order food to where the guest is sitting, or for collection.</t>
+          <t>See lost &amp; found for this venue.</t>
         </is>
       </c>
     </row>
@@ -4357,20 +4343,20 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>F&amp;B – Order Tracking</t>
+          <t>Feedback &amp; Ratings</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Watch it being made, and see the table bill; it is paid at the table.</t>
+          <t>Tell the venue how the visit went, answer a survey it sent, or report a problem.</t>
         </is>
       </c>
     </row>
@@ -4382,20 +4368,20 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Retail / Merchandise</t>
+          <t>Loyalty &amp; Rewards</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Membership, Loyalty &amp; Value</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Buy merchandise and collect it on the way out, or have it delivered home.</t>
+          <t>Your points, your tier, and what is within reach.</t>
         </is>
       </c>
     </row>
@@ -4407,20 +4393,20 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Venue Info &amp; Services</t>
+          <t>Offers &amp; Promotions</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Promotions</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>How to reach the venue, its contact details, and where to eat.</t>
+          <t>Find offers &amp; promotions for this venue.</t>
         </is>
       </c>
     </row>
@@ -4432,20 +4418,20 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Notifications</t>
+          <t>At the Venue</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>In-venue Services</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Work with in-venue notifications for this venue.</t>
+          <t>Everything live at the venue in one place: map, waits, food, shows, shop and services, with what is happening now.</t>
         </is>
       </c>
     </row>
@@ -4457,20 +4443,20 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Home</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Ask, and be answered or handed to a person.</t>
+          <t>What we hold about a guest, and what they can change.</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4468,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Chat</t>
+          <t>Help &amp; Support</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -4491,11 +4477,11 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Talk to Sahli: the answers, and a person when Sahli cannot help.</t>
+          <t>Answer a question without needing a person.</t>
         </is>
       </c>
     </row>
@@ -4507,20 +4493,20 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>AI Concierge – Contextual Help</t>
+          <t>Checkout Entry</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Cart &amp; Checkout</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Take the money, and be unambiguous about whether it worked.</t>
         </is>
       </c>
     </row>
@@ -4532,20 +4518,20 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Lost &amp; Found</t>
+          <t>Simple Registration &amp; OTP</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>See lost &amp; found for this venue.</t>
+          <t>Get a guest into the app, fast, on a device that may be shared: a one-time code to the email or mobile, a password, Apple or Google, or UAE Pass, or register a new account. **No enterprise SSO for guests** (decided 28 September, audit R167, first part). **A second factor only where the venue enabled guest two-step verification** (decided 29 September, rev 3 GAP-B1, per venue, superseding the second part of R167).</t>
         </is>
       </c>
     </row>
@@ -4557,20 +4543,20 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Loyalty &amp; Rewards</t>
+          <t>Arabic / RTL Experience</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Membership, Loyalty &amp; Value</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Your points, your tier, and what is within reach.</t>
+          <t>Choose the app's language; Arabic turns the whole app right to left.</t>
         </is>
       </c>
     </row>
@@ -4582,20 +4568,20 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Offers &amp; Promotions</t>
+          <t>Multi-Currency &amp; Pricing</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Promotions</t>
+          <t>Ticketing</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Find offers &amp; promotions for this venue.</t>
+          <t>Choose the currency you see prices in and pay in.</t>
         </is>
       </c>
     </row>
@@ -4607,20 +4593,20 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; Support</t>
+          <t>Ticket Delivery &amp; Sharing</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Answer a question without needing a person.</t>
+          <t>Find ticket delivery &amp; sharing for this venue.</t>
         </is>
       </c>
     </row>
@@ -4632,20 +4618,20 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Multi-Currency &amp; Pricing</t>
+          <t>Branded Queue / Waiting Room</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Ticketing</t>
+          <t>High-Demand Access</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Choose the currency you see prices in and pay in.</t>
+          <t>The on-sale waiting room for one performance — the guest's place, the wait, and the way on to the sale once admitted.</t>
         </is>
       </c>
     </row>
@@ -4657,20 +4643,20 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Ticket Delivery &amp; Sharing</t>
+          <t>Maintenance / Upgrade Page</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>System States</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Find ticket delivery &amp; sharing for this venue.</t>
+          <t>Say what is wrong in a way that tells the person whether to wait or leave.</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4677,7 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
@@ -4716,7 +4702,7 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
@@ -4732,7 +4718,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Bundle Package</t>
+          <t>Resource Booking – Cabana</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -4741,11 +4727,11 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>See bundle package for this venue.</t>
+          <t>Book a cabana or other capacity-based resource.</t>
         </is>
       </c>
     </row>
@@ -4757,20 +4743,20 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Information</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Discovery &amp; Browse</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Step-free routes, facilities and what to expect.</t>
+          <t>The Plan tab: tell the venue who is coming, when, at what pace and what you like, and get a day-by-day plan.</t>
         </is>
       </c>
     </row>
@@ -4782,20 +4768,20 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Menu Item Detail</t>
+          <t>Suggested Itineraries</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Decide on a dish, choose modifiers, check allergens.</t>
+          <t>Ready-made day plans for this venue that a guest can take instead of answering questions.</t>
         </is>
       </c>
     </row>
@@ -4807,20 +4793,20 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Shop &amp; Drop Collection</t>
+          <t>Your Plan</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>In-Venue Experience</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
+          <t>The plan, day by day: swap, remove or add items, undo, add Fast Track, then book the whole plan.</t>
         </is>
       </c>
     </row>
@@ -4832,20 +4818,20 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Privacy &amp; My Data</t>
+          <t>AI Planner</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
+          <t>Ask the planner in your own words to change the plan; it refines the rules plan, and the rules plan stays if AI is unavailable.</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4843,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Refunds &amp; Resale</t>
+          <t>Dynamic QR Ticket</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -4866,11 +4852,11 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
+          <t>Show the live ticket code at the gate.</t>
         </is>
       </c>
     </row>
@@ -4882,20 +4868,20 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Help &amp; My Cases</t>
+          <t>Bundle Package</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
+          <t>See bundle package for this venue.</t>
         </is>
       </c>
     </row>
@@ -4907,20 +4893,20 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Face Pass</t>
+          <t>Accessibility Information</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Discovery &amp; Browse</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Register or remove my face for gate entry on my pass, or a linked child's with my consent as guardian.</t>
+          <t>Step-free routes, facilities and what to expect.</t>
         </is>
       </c>
     </row>
@@ -4932,20 +4918,20 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Reserve a Table</t>
+          <t>Resource Availability (Cabana)</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Booking &amp; Selection</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas, loungers and other spots on a venue map are booked on GST-074 (decided 29 September, rev 3 REV3-15 and GAP-C2, superseding audit R073 (c)). A deposit only where the venue enabled one (rev 3 REV3-8b, superseding audit R077 (a)).</t>
+          <t>See which cabanas are free, by area and date, before choosing one.</t>
         </is>
       </c>
     </row>
@@ -4957,20 +4943,20 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Payment Methods</t>
+          <t>Plan in Progress</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
+          <t>Today's plan while you are in the venue, re-ordered against live waits.</t>
         </is>
       </c>
     </row>
@@ -4982,20 +4968,20 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Share &amp; Group Booking</t>
+          <t>Menu Item Detail</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
+          <t>Decide on a dish, choose modifiers, check allergens.</t>
         </is>
       </c>
     </row>
@@ -5007,20 +4993,20 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Sign-in</t>
+          <t>Shop &amp; Drop Collection</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>In-Venue Experience</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. Two-step verification where a venue of the tenant enabled it (decided 29 September, rev 3 GAP-B1, per venue).</t>
+          <t>Collect shopping left earlier, using the ticket rather than a receipt.</t>
         </is>
       </c>
     </row>
@@ -5032,20 +5018,20 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Add to Calendar / Reminders</t>
+          <t>Explore – Search Results</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Discovery</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Find add to calendar / reminders for this venue.</t>
+          <t>Find something when you do not know what it is called.</t>
         </is>
       </c>
     </row>
@@ -5057,20 +5043,20 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Saved Items / Wishlist</t>
+          <t>Newsletter &amp; Preferences</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Account &amp; Self-Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Find the right one quickly, and act on it without opening it.</t>
+          <t>What we may send you, and how.</t>
         </is>
       </c>
     </row>
@@ -5082,20 +5068,20 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Virtual Queue</t>
+          <t>Privacy &amp; My Data</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Hold a place in a ride queue without standing in it.</t>
+          <t>**A guest can legally demand their data and its erasure, and had nowhere to ask.** `exportSubjectData` and `deleteGuestAccount` existed as guest-callable operations reachable from no guest surface — a</t>
         </is>
       </c>
     </row>
@@ -5107,20 +5093,20 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reserve &amp; Pay</t>
+          <t>Refunds &amp; Resale</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Choose a car park and add parking to the basket; change the plate on parking already bought.</t>
+          <t>**A guest could buy a ticket and not ask for their money back.** `createRefundRequest` and `createResaleListing` were back-office only, so every refund began as a phone call.</t>
         </is>
       </c>
     </row>
@@ -5132,20 +5118,20 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Parking – Reservation Confirmed</t>
+          <t>Help &amp; My Cases</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>In-venue Services</t>
+          <t>Engagement &amp; Support</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Confirm it worked, and give them what they need to prove it.</t>
+          <t>**A guest could not raise a complaint.** Twelve case operations existed and every one of them was staff-side — a guest with a problem had to find somebody.</t>
         </is>
       </c>
     </row>
@@ -5157,20 +5143,20 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Feedback &amp; Ratings</t>
+          <t>Face Pass</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Engagement &amp; Support</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Tell the venue how the visit went, answer a survey it sent, or report a problem.</t>
+          <t>Register or remove my face for gate entry on my pass, or a linked child's with my consent as guardian.</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5168,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>At the Venue</t>
+          <t>Reserve a Table</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -5191,11 +5177,11 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Everything live at the venue in one place: map, waits, food, shows, shop and services, with what is happening now.</t>
+          <t>**Book a restaurant table, or wait for one.** A guest reserves a table ahead, changes or cancels it, or joins and leaves a restaurant's waitlist. Tables only: cabanas, loungers and other spots on a venue map are booked on GST-074 (decided 29 September, rev 3 REV3-15 and GAP-C2, superseding audit R073 (c)). A deposit only where the venue enabled one (rev 3 REV3-8b, superseding audit R077 (a)).</t>
         </is>
       </c>
     </row>
@@ -5207,20 +5193,20 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Resource Booking – Cabana</t>
+          <t>Payment Methods</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Booking &amp; Selection</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Book a cabana or other capacity-based resource.</t>
+          <t>**A stored card a guest cannot see is a stored card they cannot remove.** `listPaymentTokens` and `storePaymentToken` were guest-callable with no guest screen.</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5218,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Resource Availability (Cabana)</t>
+          <t>Share &amp; Group Booking</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -5241,11 +5227,11 @@
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>See which cabanas are free, by area and date, before choosing one.</t>
+          <t>**A guest buying eight tickets could not give seven of them away.** `shareEntitlement`, `getGroupBooking` and `respondToInvitation` had no surface, so a group booking was one person holding eight barc</t>
         </is>
       </c>
     </row>
@@ -5257,20 +5243,20 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Newsletter &amp; Preferences</t>
+          <t>Security &amp; Sign-in</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Account &amp; Self-Service</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>What we may send you, and how.</t>
+          <t>**How this guest signs in, and where.** The sign-in methods linked to the account, the email that recovers it, and the devices signed in, with a way to sign a lost phone out. Small screen, and it is the one a guest reaches after losing a phone. Two-step verification where a venue of the tenant enabled it (decided 29 September, rev 3 GAP-B1, per venue).</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5277,7 @@
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
@@ -5316,7 +5302,7 @@
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
@@ -5341,7 +5327,7 @@
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5352,7 @@
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
@@ -5391,7 +5377,7 @@
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
@@ -5416,7 +5402,7 @@
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -5432,12 +5418,12 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Site Builder</t>
+          <t>White-Label Branding Management</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
@@ -5445,7 +5431,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Build a working site in about 30 minutes: pick a preset, then walk seven saved steps (venue and modules, ticketing flows, compose steps, Help me choose, look and feel, mobile app, preview and publish), each opening the full screen for its details. **The preset keeps the minimum path short (M24-05)**: it proposes the modules, the booking flows with their default step order, the home sections and the mobile tabs, so the only things an operator must supply are a logo, four colours and a Publish; everything else keeps the preset or the contract default and can be refined later.</t>
+          <t>Support a tenant's branding from the platform console, inside an open grant.</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5443,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Booking Flows</t>
+          <t>Domain &amp; Certificate Management</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
@@ -5470,7 +5456,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Pick the venue's booking flows, turn optional steps on or off, set the step order within the allowed limits with a live preview, assign flows to products and categories, and validate them before they publish with the site.</t>
+          <t>Support a tenant's custom domains and certificates from the platform console.</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5468,12 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>App Build &amp; Store Publishing</t>
+          <t>Interface Languages</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>White Label</t>
+          <t>Branding &amp; Localisation</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
@@ -5495,7 +5481,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Get the tenant's own app into the App Store and Google Play under the client's own accounts — checklist, store listing, request a build, download or submit it, follow its review — with a guide for the steps only the client can take.</t>
+          <t>Add or select a tenant's interface languages beyond English and Arabic, inside an open grant, and see how far the interface strings reach in each.</t>
         </is>
       </c>
     </row>
@@ -5507,20 +5493,20 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>White-Label Branding Management</t>
+          <t>Module Activation &amp; Dependency Validation</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>Tenants &amp; Licensing</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Support a tenant's branding from the platform console, inside an open grant.</t>
+          <t>Activate the modules purchased in Board 4/5 and verify all required dependencies.</t>
         </is>
       </c>
     </row>
@@ -5532,20 +5518,20 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate Management</t>
+          <t>Tenant Workspace</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Support a tenant's custom domains and certificates from the platform console.</t>
+          <t>Land a tenant somewhere that shows what is live and what is not, and hold step 1 of the Site Builder (venue and modules).</t>
         </is>
       </c>
     </row>
@@ -5557,20 +5543,20 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Interface Languages</t>
+          <t>Brand Kit</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Branding &amp; Localisation</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Add or select a tenant's interface languages beyond English and Arabic, inside an open grant, and see how far the interface strings reach in each.</t>
+          <t>Set the things every surface reads.</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5568,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Tenant Workspace</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -5591,11 +5577,11 @@
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Land a tenant somewhere that shows what is live and what is not, and hold step 1 of the Site Builder (venue and modules).</t>
+          <t>Choose the two typefaces, Latin and Arabic; the type scale is TICVAI's fixed token set.</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5593,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Brand Kit</t>
+          <t>Logo &amp; Assets</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -5616,11 +5602,11 @@
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Set the things every surface reads.</t>
+          <t>Hold the marks every surface needs, at the sizes it needs them, and the mobile app's intro video (Site Builder steps 5 and 6).</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5618,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Theme Editor</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -5641,11 +5627,11 @@
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Choose the two typefaces, Latin and Arabic; the type scale is TICVAI's fixed token set.</t>
+          <t>Tune the theme and watch it apply everywhere at once.</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5643,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Logo &amp; Assets</t>
+          <t>Component Preview</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -5666,11 +5652,11 @@
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Hold the marks every surface needs, at the sizes it needs them, and the mobile app's intro video (Site Builder steps 5 and 6).</t>
+          <t>Check the theme against the components that carry it.</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5668,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Theme Editor</t>
+          <t>Page Builder</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -5691,11 +5677,11 @@
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Tune the theme and watch it apply everywhere at once.</t>
+          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5693,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Component Preview</t>
+          <t>Content Blocks</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -5716,11 +5702,11 @@
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Check the theme against the components that carry it.</t>
+          <t>Define what a block can and cannot contain, and set the banners (Site Builder step 5).</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5718,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Page Builder</t>
+          <t>Navigation &amp; Menus</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -5741,11 +5727,11 @@
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Assemble a storefront page from blocks the tenant cannot break.</t>
+          <t>Three editors, each saved on its own: the header, the footer and the mobile tab bar with the Buy tickets button (Site Builder steps 5 and 6); and the links a tenant's own site uses to deep-link in.</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5743,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Content Blocks</t>
+          <t>Media Library</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -5766,11 +5752,11 @@
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Define what a block can and cannot contain, and set the banners (Site Builder step 5).</t>
+          <t>Hold the imagery, and know where it is used.</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5768,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Navigation &amp; Menus</t>
+          <t>Translations</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -5791,11 +5777,11 @@
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Three editors, each saved on its own: the header, the footer and the mobile tab bar with the Buy tickets button (Site Builder steps 5 and 6); and the links a tenant's own site uses to deep-link in.</t>
+          <t>Fill in what every language is missing.</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5793,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Media Library</t>
+          <t>RTL Preview</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -5816,11 +5802,11 @@
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Hold the imagery, and know where it is used.</t>
+          <t>See the site as an Arabic reader sees it.</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5818,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Translations</t>
+          <t>SEO &amp; Metadata</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -5841,11 +5827,11 @@
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Fill in what every language is missing.</t>
+          <t>Control how a page looks everywhere it is not the page.</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5843,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>RTL Preview</t>
+          <t>Publishing Workflow</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -5866,11 +5852,11 @@
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>See the site as an Arabic reader sees it.</t>
+          <t>Move a change from draft to live, with someone accountable (Site Builder step 7).</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5868,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>SEO &amp; Metadata</t>
+          <t>Version History</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -5891,11 +5877,11 @@
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Control how a page looks everywhere it is not the page.</t>
+          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5893,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Publishing Workflow</t>
+          <t>Site Settings</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -5916,11 +5902,11 @@
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Move a change from draft to live, with someone accountable (Site Builder step 7).</t>
+          <t>The values the whole site inherits from, and the venue-wide booking settings each venue may override (decided 29 September, rev 3 CFG-11); the settings of one flow are on CMS-103 (W12).</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5918,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Version History</t>
+          <t>Domain &amp; Certificate</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -5941,11 +5927,11 @@
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>See who changed what and go back if it was wrong — by restoring into the draft, reviewing, then publishing.</t>
+          <t>Point the tenant’s own domain at their site.</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5943,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Site Settings</t>
+          <t>Consent &amp; Legal</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -5966,11 +5952,11 @@
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>The values the whole site inherits from, and the venue-wide booking settings each venue may override (decided 29 September, rev 3 CFG-11); the settings of one flow are on CMS-103 (W12).</t>
+          <t>Manage the notices every consent is captured against, and the booking consent questions a venue asks ("Are you able to swim?", "I accept the risk"), with the record of every answer (decided 29 September, rev 3 REV3-26).</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5968,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Domain &amp; Certificate</t>
+          <t>User Access</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -5991,11 +5977,11 @@
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Point the tenant’s own domain at their site.</t>
+          <t>Say who in the tenant may change what.</t>
         </is>
       </c>
     </row>
@@ -6007,7 +5993,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Consent &amp; Legal</t>
+          <t>Help Me Choose</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -6016,11 +6002,11 @@
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Manage the notices every consent is captured against, and the booking consent questions a venue asks ("Are you able to swim?", "I accept the risk"), with the record of every answer (decided 29 September, rev 3 REV3-26).</t>
+          <t>Set up a venue's Help me choose so its answers filter the catalogue, review the question set the assistant proposes from the venue's products, preview the filtered list and publish it (Site Builder step 4).</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6018,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>User Access</t>
+          <t>Site Builder</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -6041,11 +6027,11 @@
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Say who in the tenant may change what.</t>
+          <t>Build a working site in about 30 minutes: pick a preset, then walk seven saved steps (venue and modules, ticketing flows, compose steps, Help me choose, look and feel, mobile app, preview and publish), each opening the full screen for its details. **The preset keeps the minimum path short (M24-05)**: it proposes the modules, the booking flows with their default step order, the home sections and the mobile tabs, so the only things an operator must supply are a logo, four colours and a Publish; everything else keeps the preset or the contract default and can be refined later.</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6043,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Help Me Choose</t>
+          <t>Booking Flows</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -6066,11 +6052,11 @@
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Set up a venue's Help me choose so its answers filter the catalogue, review the question set the assistant proposes from the venue's products, preview the filtered list and publish it (Site Builder step 4).</t>
+          <t>Pick the venue's booking flows, turn optional steps on or off, set the step order within the allowed limits with a live preview, assign flows to products and categories, and validate them before they publish with the site.</t>
         </is>
       </c>
     </row>
@@ -6082,20 +6068,20 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Module Activation &amp; Dependency Validation</t>
+          <t>App Build &amp; Store Publishing</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Tenants &amp; Licensing</t>
+          <t>White Label</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Activate the modules purchased in Board 4/5 and verify all required dependencies.</t>
+          <t>Get the tenant's own app into the App Store and Google Play under the client's own accounts — checklist, store listing, request a build, download or submit it, follow its review — with a guide for the steps only the client can take.</t>
         </is>
       </c>
     </row>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -792,17 +792,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Wallets and credit</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Guest wallets, stored credit, gift cards and membership credit.</t>
+          <t>The financial record of every sale, refund and payment, and currency rates.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Wallet balances cannot be spent until it returns.</t>
+          <t>Finance postings wait until it returns; trading is not affected.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -825,17 +825,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Wallets and credit</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The financial record of every sale, refund and payment, and currency rates.</t>
+          <t>Guest wallets, stored credit, gift cards and membership credit.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Finance postings wait until it returns; trading is not affected.</t>
+          <t>Wallet balances cannot be spent until it returns.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -858,17 +858,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Venue operations</t>
+          <t>Food and beverage</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Queues and wait times, maintenance, bookable resources, the venue map and media.</t>
+          <t>Menus, table service, kitchen screens and food orders.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Venue operations degrade; selling and entry continue.</t>
+          <t>Kitchens fall back to printed tickets.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -886,26 +886,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
+          <t>Venue operations</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Menus, table service, kitchen screens and food orders.</t>
+          <t>Queues and wait times, maintenance, bookable resources, the venue map and media.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kitchens fall back to printed tickets.</t>
+          <t>Venue operations degrade; selling and entry continue.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -923,7 +919,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -1756,7 +1756,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Omnichannel Order &amp; Fulfilment Center — from the client design board, 20 August.</t>
+          <t>Hand over the orders waiting at this outlet (takeaway, delivery and collection), reserve merchandise for a guest to collect, and hand dropped goods back to the guest.</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sales Exceptions, Controls &amp; Operational Actions — from the client design board, 20 August.</t>
+          <t>Handle the till's exceptions on an order: open the drawer without a sale, with a reason, void an order, or apply a manual discount.</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Cash In / Cash Out Operations — from the client design board, 20 August.</t>
+          <t>Record cash added to or lifted from the drawer during the shift, counted by denomination and with a reason, against the shift's movements so far.</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Shift Exceptions &amp; Alerts — from the client design board, 20 August.</t>
+          <t>Work the shift's alerts and the approval requests waiting for this supervisor, decide them, and record a no-sale.</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>See add-ons &amp; upsell for this venue.</t>
+          <t>Suggested add-ons and the offered bundle for this booking, each added to the cart, before checkout.</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>The guest's tickets and passes, current and past: each with its code and history, sent to another guest, shared, or added to a phone wallet.</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Find order history for this venue.</t>
+          <t>The guest's orders: open one, ask for a refund, and get or download its tax invoice and credit notes.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>See wallet &amp; gift cards for this venue.</t>
+          <t>The guest's wallet and its activity, saved cards, and the balance on a gift card or game card.</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Work with membership management for this venue.</t>
+          <t>The guest's membership: billing statements, payments that need them, and the membership itself.</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Find contact &amp; venue information for this venue.</t>
+          <t>How to reach the venue: phone, email, address and opening hours, readable without signing in.</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Find what's on for this venue.</t>
+          <t>What is on at this venue over the dates the guest picks: each performance and the products that run.</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>See event / exhibition details for this venue.</t>
+          <t>One event or exhibition: what it is, and the performance being booked, before choosing tickets.</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Find my tickets for this venue.</t>
+          <t>The guest's tickets and passes, current and past: open one to see its code and history, or send it to another guest.</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Find ticket details for this venue.</t>
+          <t>One ticket: its code to scan, what remains on it and every scan against it; send it to another guest or bind it to this phone.</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Work with ticket transfer for this venue.</t>
+          <t>Send tickets from one of the guest's orders to another guest, and claim tickets someone sent.</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Find memberships for this venue.</t>
+          <t>The guest's membership: plans, statements, payments that need them, and family members who may use it.</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Find my reservations for this venue.</t>
+          <t>The guest's reservations, each opened to see it or cancel it.</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>See reservation details for this venue.</t>
+          <t>One reservation, read and cancellable.</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Find add to calendar / reminders for this venue.</t>
+          <t>Put a booked visit in the phone's calendar or wallet, and turn its visit reminder on or off.</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>See attraction wait times for this venue.</t>
+          <t>How long each attraction's queue is right now.</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Work with in-venue notifications for this venue.</t>
+          <t>The guest's in-venue notifications, newest first: queue calls, order ready, booking changes and venue alerts, marked read once seen.</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>See lost &amp; found for this venue.</t>
+          <t>Report a lost item, follow the guest's lost-property cases and reply on them.</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Find offers &amp; promotions for this venue.</t>
+          <t>The offers running at this venue, one opened in detail, and a code the guest typed checked.</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Find ticket delivery &amp; sharing for this venue.</t>
+          <t>Send some of the guest's tickets to someone else, and see the tickets sent and received.</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>See upsell / cross-sell for this venue.</t>
+          <t>Suggestions for the cart the guest is about to pay for, each added with one tap.</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>See interactive seat selection for this venue.</t>
+          <t>Pick seats on the seat map for the chosen performance, or let the venue recommend them, and hold them.</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>See bundle package for this venue.</t>
+          <t>One bundle: what it includes and its price, added to the cart.</t>
         </is>
       </c>
     </row>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -722,17 +722,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Products and pricing</t>
+          <t>Entry and admission</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>What is sold, at what price and when: products, events and sessions, price lists, promotions, bundles and seating.</t>
+          <t>Tickets and passes at the gate, admission rules and entry validation.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Tills keep selling from their last published catalogue; changes wait.</t>
+          <t>Gates fall back to their local copy of what is valid.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -750,26 +750,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Entry and admission</t>
+          <t>Products and pricing</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tickets and passes at the gate, admission rules and entry validation.</t>
+          <t>What is sold, at what price and when: products, events and sessions, price lists, promotions, bundles and seating.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Gates fall back to their local copy of what is valid.</t>
+          <t>Tills keep selling from their last published catalogue; changes wait.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -787,22 +783,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Wallets and credit</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The financial record of every sale, refund and payment, and currency rates.</t>
+          <t>Guest wallets, stored credit, gift cards and membership credit.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Finance postings wait until it returns; trading is not affected.</t>
+          <t>Wallet balances cannot be spent until it returns.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -825,17 +825,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Wallets and credit</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Guest wallets, stored credit, gift cards and membership credit.</t>
+          <t>The financial record of every sale, refund and payment, and currency rates.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Wallet balances cannot be spent until it returns.</t>
+          <t>Finance postings wait until it returns; trading is not affected.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>My wallet: balance, activity and auto top-up, and what is due or refundable at exit.</t>
+          <t>My wallet: balance, activity and auto top-up.</t>
         </is>
       </c>
     </row>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/service-docs/TICVAI_First_Release_Client.xlsx
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Everything I have with this venue at a glance: bookings, wallet, loyalty, challenges and invitations, each opening its own pane.</t>
+          <t>Everything I have with this venue at a glance: my membership and its rewards balance, my next bookings as tickets, my challenges, wallet, orders and invitations, each opening its own pane.</t>
         </is>
       </c>
     </row>
